--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_43.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3447333.223563921</v>
+        <v>3448469.841540288</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13609380.65600007</v>
+        <v>13633690.08805684</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13609380.65600007</v>
+        <v>13633690.08805684</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133313.3644571714</v>
+        <v>143186.9484571429</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133313.3644571714</v>
+        <v>143186.9484571429</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24189478.44946488</v>
+        <v>24188492.70050179</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.347322035758888</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.798687867827562</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,67 +733,67 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>209.4985557026693</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>144.7989632036872</v>
+      </c>
+      <c r="R3" t="n">
+        <v>133.5184388018132</v>
+      </c>
+      <c r="S3" t="n">
+        <v>62.44885845517734</v>
+      </c>
+      <c r="T3" t="n">
         <v>374</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>287.6071237589809</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>145.073529241423</v>
-      </c>
-      <c r="R3" t="n">
-        <v>133.6519859716245</v>
-      </c>
-      <c r="S3" t="n">
-        <v>62.48881128536601</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.473444462796863</v>
-      </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>100.720585996287</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.798687867826661</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -988,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,31 +1015,31 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>171.3595218932716</v>
       </c>
       <c r="W6" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>130.2703938077541</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>5.296708396048877</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,28 +1207,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>249.1703537962586</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>156.8488547017515</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
@@ -1459,10 +1459,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H12" t="n">
-        <v>5.417475575159462</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I12" t="n">
         <v>191.2065745705938</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.532287858417</v>
+        <v>181.0524309641367</v>
       </c>
       <c r="S12" t="n">
         <v>131.5805093985736</v>
@@ -1504,7 +1504,7 @@
         <v>79.16083145829998</v>
       </c>
       <c r="V12" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>111.3731429098285</v>
@@ -1620,10 +1620,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H14" t="n">
-        <v>72.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.388898923102739</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.388898923102697</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>141.7853537319712</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T14" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U14" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1687,7 +1687,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
@@ -1696,13 +1696,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H15" t="n">
-        <v>3.897332469440016</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,19 +1729,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.532287858417</v>
+        <v>181.0524309641367</v>
       </c>
       <c r="S15" t="n">
         <v>131.5805093985736</v>
       </c>
       <c r="T15" t="n">
-        <v>402.3233312552497</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U15" t="n">
-        <v>271.8875491346126</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>111.3731429098285</v>
@@ -1750,7 +1750,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M16" t="n">
         <v>100.6963655009106</v>
@@ -1811,7 +1811,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S16" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,10 +1857,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H17" t="n">
-        <v>72.59985970855251</v>
+        <v>73.98875863165527</v>
       </c>
       <c r="I17" t="n">
-        <v>1.388898923102767</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>219.6644045740158</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>214.3988148982257</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
@@ -1978,7 +1978,7 @@
         <v>79.16083145829998</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
@@ -1987,7 +1987,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2097,7 +2097,7 @@
         <v>72.59985970855251</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.388898923102767</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.388898923102697</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>141.7853537319712</v>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>256.2832743226397</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>219.6644045740158</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>3.986705686348103</v>
@@ -2224,7 +2224,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2331,10 +2331,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H23" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I23" t="n">
-        <v>1.388898923102739</v>
+        <v>1.388898923102767</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T23" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U23" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V23" t="n">
         <v>308.8510241668239</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>232.8266301218324</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H24" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2446,19 +2446,19 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T24" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>304.0998605861415</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M25" t="n">
         <v>100.6963655009106</v>
@@ -2522,7 +2522,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S25" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H26" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,16 +2598,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.388898923102697</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S26" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T26" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2632,7 +2632,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>232.8266301218327</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
@@ -2641,13 +2641,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H27" t="n">
-        <v>3.897332469439999</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.532287858417</v>
+        <v>372.2590055347304</v>
       </c>
       <c r="S27" t="n">
-        <v>452.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T27" t="n">
-        <v>81.32333125524967</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2695,7 +2695,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M28" t="n">
         <v>100.6963655009106</v>
@@ -2759,7 +2759,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S28" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.388898923102697</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S29" t="n">
         <v>141.7853537319712</v>
@@ -2866,28 +2866,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.986705686348103</v>
       </c>
       <c r="H30" t="n">
-        <v>3.897332469440016</v>
+        <v>119.6428982628208</v>
       </c>
       <c r="I30" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,13 +2911,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R30" t="n">
-        <v>181.0524309641363</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S30" t="n">
-        <v>452.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T30" t="n">
         <v>81.32333125524968</v>
@@ -2929,7 +2929,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>98.86273944538755</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.388898923102697</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S32" t="n">
         <v>141.7853537319711</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>256.28327432264</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>155.8454782389002</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
@@ -3118,7 +3118,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>3.986705686348098</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H33" t="n">
         <v>3.897332469439999</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R33" t="n">
         <v>179.532287858417</v>
@@ -3157,7 +3157,7 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T33" t="n">
-        <v>402.3233312552497</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U33" t="n">
         <v>79.16083145829995</v>
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>137.9993129555745</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>105.4745782429939</v>
+        <v>104.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>66.33915573984979</v>
+        <v>65.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>60.36328960686865</v>
+        <v>59.36328960686865</v>
       </c>
       <c r="F35" t="n">
-        <v>60.88962870801186</v>
+        <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>58.35033711113682</v>
+        <v>57.35033711113682</v>
       </c>
       <c r="H35" t="n">
-        <v>49.59985970855254</v>
+        <v>48.59985970855254</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,28 +3309,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>-2.115939423674717e-11</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>118.7853537319711</v>
+        <v>117.7853537319711</v>
       </c>
       <c r="T35" t="n">
-        <v>236.5162852461518</v>
+        <v>235.5162852461518</v>
       </c>
       <c r="U35" t="n">
-        <v>305.1087337345403</v>
+        <v>292.2256326576843</v>
       </c>
       <c r="V35" t="n">
-        <v>285.8510241668239</v>
+        <v>284.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>287.8943749041154</v>
+        <v>293.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>248.2818334606677</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>167.3174326828064</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>98.01900783741002</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.384892622237</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R36" t="n">
-        <v>156.532287858417</v>
+        <v>155.532287858417</v>
       </c>
       <c r="S36" t="n">
-        <v>452.5805093985736</v>
+        <v>107.5805093985736</v>
       </c>
       <c r="T36" t="n">
-        <v>402.3233312552497</v>
+        <v>57.32333125524966</v>
       </c>
       <c r="U36" t="n">
-        <v>56.16083145829995</v>
+        <v>55.16083145829995</v>
       </c>
       <c r="V36" t="n">
-        <v>70.51066719152016</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>88.37314290982852</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>75.86273944538755</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>55.39139276613435</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>77.69636550091056</v>
+        <v>76.69636550091056</v>
       </c>
       <c r="N37" t="n">
-        <v>130.602288386439</v>
+        <v>129.602288386439</v>
       </c>
       <c r="O37" t="n">
-        <v>207.2357280134412</v>
+        <v>206.2357280134412</v>
       </c>
       <c r="P37" t="n">
-        <v>267.1134710987693</v>
+        <v>266.1134710987693</v>
       </c>
       <c r="Q37" t="n">
-        <v>328.989266425598</v>
+        <v>327.989266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>354.2234394565609</v>
+        <v>353.2234394565609</v>
       </c>
       <c r="S37" t="n">
-        <v>7.374299374986586</v>
+        <v>6.374299374986586</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>137.9993129555745</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>105.4745782429939</v>
+        <v>104.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>66.33915573984979</v>
+        <v>65.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>60.36328960686865</v>
+        <v>59.36328960686865</v>
       </c>
       <c r="F38" t="n">
-        <v>60.88962870801186</v>
+        <v>59.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>51.87123603428352</v>
+        <v>57.35033711113682</v>
       </c>
       <c r="H38" t="n">
-        <v>49.59985970855254</v>
+        <v>48.59985970855254</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,25 +3549,25 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>118.7853537319711</v>
+        <v>105.902252655173</v>
       </c>
       <c r="T38" t="n">
-        <v>236.5162852461518</v>
+        <v>235.5162852461518</v>
       </c>
       <c r="U38" t="n">
-        <v>305.1087337345403</v>
+        <v>304.1087337345403</v>
       </c>
       <c r="V38" t="n">
-        <v>285.8510241668239</v>
+        <v>284.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>294.3734759809475</v>
+        <v>293.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>248.2818334606677</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>167.3174326828064</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.55655664632661</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>17.09991244551929</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>3.937686897702633</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,31 +3622,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R39" t="n">
-        <v>156.532287858417</v>
+        <v>155.532287858417</v>
       </c>
       <c r="S39" t="n">
-        <v>108.5805093985736</v>
+        <v>107.5805093985736</v>
       </c>
       <c r="T39" t="n">
-        <v>402.3233312552497</v>
+        <v>57.32333125524966</v>
       </c>
       <c r="U39" t="n">
-        <v>56.16083145829995</v>
+        <v>400.1608314583</v>
       </c>
       <c r="V39" t="n">
-        <v>70.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>326.4494213932488</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>411.9197292895946</v>
       </c>
       <c r="Y39" t="n">
-        <v>55.39139276613435</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3689,25 +3689,25 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>77.69636550091056</v>
+        <v>76.69636550091056</v>
       </c>
       <c r="N40" t="n">
-        <v>130.602288386439</v>
+        <v>129.602288386439</v>
       </c>
       <c r="O40" t="n">
-        <v>207.2357280134412</v>
+        <v>206.2357280134412</v>
       </c>
       <c r="P40" t="n">
-        <v>267.1134710987693</v>
+        <v>266.1134710987693</v>
       </c>
       <c r="Q40" t="n">
-        <v>328.989266425598</v>
+        <v>327.989266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>354.2234394565609</v>
+        <v>353.2234394565609</v>
       </c>
       <c r="S40" t="n">
-        <v>7.374299374986586</v>
+        <v>6.374299374986586</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
         <v>81.35033711113681</v>
       </c>
       <c r="H41" t="n">
-        <v>72.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>141.7853537319712</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>259.5162852461518</v>
+        <v>181.8931161443186</v>
       </c>
       <c r="U41" t="n">
-        <v>211.9938396086922</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V41" t="n">
         <v>308.8510241668239</v>
@@ -3817,25 +3817,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H42" t="n">
-        <v>196.6240501457532</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R42" t="n">
-        <v>179.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S42" t="n">
-        <v>131.5805093985736</v>
+        <v>358.2385469566094</v>
       </c>
       <c r="T42" t="n">
-        <v>81.32333125524968</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M43" t="n">
         <v>100.6963655009106</v>
@@ -3944,7 +3944,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S43" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3978,10 +3978,10 @@
         <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F44" t="n">
         <v>83.88962870801186</v>
@@ -4026,10 +4026,10 @@
         <v>141.7853537319711</v>
       </c>
       <c r="T44" t="n">
-        <v>259.5162852461518</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>172.332078004405</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V44" t="n">
         <v>308.8510241668239</v>
@@ -4041,7 +4041,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>190.3174326828064</v>
+        <v>101.95061685216</v>
       </c>
     </row>
     <row r="45">
@@ -4057,19 +4057,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>245.294279895912</v>
       </c>
       <c r="G45" t="n">
-        <v>3.986705686348098</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H45" t="n">
-        <v>3.897332469439999</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I45" t="n">
         <v>191.2065745705938</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.520143105719594</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R45" t="n">
         <v>179.532287858417</v>
@@ -4117,7 +4117,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
         <v>78.39139276613435</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375083</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.93982591751335</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426109942</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183816</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485649</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,52 +4321,52 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>451.8183303517587</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L2" t="n">
-        <v>822.0783303517587</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N2" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.183143567851</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606416</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178447</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698508</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861903</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165462</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138516</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190976</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>320.4322462211928</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="C3" t="n">
-        <v>320.4322462211928</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="D3" t="n">
-        <v>320.4322462211928</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="E3" t="n">
-        <v>320.4322462211928</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="F3" t="n">
-        <v>320.4322462211928</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="G3" t="n">
-        <v>320.4322462211928</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="H3" t="n">
-        <v>29.92</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>174.3973709300159</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>398.6635894772295</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>717.174568996958</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>858.2892107398172</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1492.786030368536</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1211.245105910912</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1148.125094511552</v>
+        <v>1151.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1143.60646374105</v>
+        <v>774.0138783225477</v>
       </c>
       <c r="U3" t="n">
-        <v>1143.408558894664</v>
+        <v>396.2361005447699</v>
       </c>
       <c r="V3" t="n">
-        <v>1128.75131930727</v>
+        <v>294.4981348919547</v>
       </c>
       <c r="W3" t="n">
-        <v>1096.051174953908</v>
+        <v>261.7979905385926</v>
       </c>
       <c r="X3" t="n">
-        <v>1075.987801776748</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="Y3" t="n">
-        <v>698.2100239989707</v>
+        <v>241.7346173614335</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>394.0960360187381</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="C4" t="n">
-        <v>394.0960360187381</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="D4" t="n">
-        <v>394.0960360187381</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="E4" t="n">
-        <v>511.9249402301512</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="F4" t="n">
-        <v>636.2859128220866</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="G4" t="n">
-        <v>789.8745737909392</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="H4" t="n">
-        <v>789.8745737909392</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.483548464727</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
         <v>29.92</v>
@@ -4509,22 +4509,22 @@
         <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U4" t="n">
-        <v>276.481125097303</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="V4" t="n">
-        <v>276.481125097303</v>
+        <v>664.1639650109064</v>
       </c>
       <c r="W4" t="n">
-        <v>276.481125097303</v>
+        <v>836.0548832705838</v>
       </c>
       <c r="X4" t="n">
-        <v>276.481125097303</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="Y4" t="n">
-        <v>282.338698352446</v>
+        <v>987.0856742947773</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,52 +4558,52 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>327.128108133742</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L5" t="n">
-        <v>697.388108133742</v>
+        <v>452.4242787922349</v>
       </c>
       <c r="M5" t="n">
-        <v>697.388108133742</v>
+        <v>822.6842787922349</v>
       </c>
       <c r="N5" t="n">
-        <v>697.388108133742</v>
+        <v>1192.944278792235</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1192.944278792235</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1251.608485181106</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1494.183143567852</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241.6095073802453</v>
+        <v>921.0301624906265</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6095073802453</v>
+        <v>921.0301624906265</v>
       </c>
       <c r="D6" t="n">
-        <v>241.6095073802453</v>
+        <v>921.0301624906265</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>973.7936800211478</v>
       </c>
       <c r="W6" t="n">
-        <v>750.973541529492</v>
+        <v>941.0935356677857</v>
       </c>
       <c r="X6" t="n">
-        <v>619.3872851580231</v>
+        <v>921.0301624906265</v>
       </c>
       <c r="Y6" t="n">
-        <v>241.6095073802453</v>
+        <v>921.0301624906265</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>828.6802319128404</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="C7" t="n">
-        <v>954.6822377312762</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="D7" t="n">
-        <v>1068.001381856276</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="E7" t="n">
-        <v>1068.001381856276</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="F7" t="n">
-        <v>1192.362354448212</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="G7" t="n">
-        <v>1192.362354448212</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="H7" t="n">
-        <v>1363.497930427282</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="I7" t="n">
-        <v>1363.497930427282</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7585226289696</v>
+        <v>43.63469300754141</v>
       </c>
       <c r="V7" t="n">
-        <v>505.7585226289696</v>
+        <v>242.4560858934874</v>
       </c>
       <c r="W7" t="n">
-        <v>677.649440888647</v>
+        <v>414.3470041531648</v>
       </c>
       <c r="X7" t="n">
-        <v>828.6802319128404</v>
+        <v>565.3777951773583</v>
       </c>
       <c r="Y7" t="n">
-        <v>828.6802319128404</v>
+        <v>676.7870958563906</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L8" t="n">
-        <v>834.5019149748742</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="M8" t="n">
-        <v>1204.761914974874</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N8" t="n">
-        <v>1204.761914974874</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1204.761914974874</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>593.0617163678237</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="C9" t="n">
-        <v>593.0617163678237</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="D9" t="n">
-        <v>241.6095073802453</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="E9" t="n">
-        <v>241.6095073802453</v>
+        <v>733.3299175207667</v>
       </c>
       <c r="F9" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="G9" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="H9" t="n">
-        <v>241.6095073802453</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V9" t="n">
-        <v>1275.29023773295</v>
+        <v>1132.226866588574</v>
       </c>
       <c r="W9" t="n">
-        <v>1242.590093379587</v>
+        <v>1099.526722235211</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="Y9" t="n">
-        <v>844.7489424246505</v>
+        <v>1079.463349058052</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>372.1048743429245</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="C10" t="n">
-        <v>372.1048743429245</v>
+        <v>385.2381431861678</v>
       </c>
       <c r="D10" t="n">
-        <v>485.4240184679246</v>
+        <v>498.5572873111679</v>
       </c>
       <c r="E10" t="n">
-        <v>603.2529226793376</v>
+        <v>573.9477435615022</v>
       </c>
       <c r="F10" t="n">
-        <v>727.6138952712731</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G10" t="n">
-        <v>881.2025562401257</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H10" t="n">
-        <v>881.2025562401257</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I10" t="n">
-        <v>881.2025562401257</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>70.34367574991084</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U10" t="n">
-        <v>70.34367574991084</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="V10" t="n">
-        <v>269.1650686358568</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="W10" t="n">
-        <v>269.1650686358568</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="X10" t="n">
-        <v>372.1048743429245</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="Y10" t="n">
-        <v>372.1048743429245</v>
+        <v>259.2361373677321</v>
       </c>
     </row>
     <row r="11">
@@ -5035,19 +5035,19 @@
         <v>561.4552612788618</v>
       </c>
       <c r="K11" t="n">
-        <v>738.645610525093</v>
+        <v>1203.965261278862</v>
       </c>
       <c r="L11" t="n">
-        <v>958.4659070075052</v>
+        <v>1423.785557761274</v>
       </c>
       <c r="M11" t="n">
-        <v>1145.826488868301</v>
+        <v>1588.310595394003</v>
       </c>
       <c r="N11" t="n">
-        <v>1788.336488868301</v>
+        <v>2230.820595394003</v>
       </c>
       <c r="O11" t="n">
-        <v>1953.49</v>
+        <v>2395.974106525702</v>
       </c>
       <c r="P11" t="n">
         <v>2596</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1011.472216904154</v>
+        <v>1009.936718817569</v>
       </c>
       <c r="C12" t="n">
-        <v>970.9672548379733</v>
+        <v>969.4317567513879</v>
       </c>
       <c r="D12" t="n">
-        <v>943.7574700928192</v>
+        <v>617.9795477638095</v>
       </c>
       <c r="E12" t="n">
-        <v>597.6240385555336</v>
+        <v>271.846116226524</v>
       </c>
       <c r="F12" t="n">
-        <v>578.799551345557</v>
+        <v>253.0216290165474</v>
       </c>
       <c r="G12" t="n">
-        <v>250.5301516623771</v>
+        <v>248.9946535757918</v>
       </c>
       <c r="H12" t="n">
         <v>245.057954111711</v>
@@ -5135,28 +5135,28 @@
         <v>2262.271670368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2080.925925057003</v>
+        <v>2079.390426970418</v>
       </c>
       <c r="S12" t="n">
-        <v>1948.016319603899</v>
+        <v>1946.480821517313</v>
       </c>
       <c r="T12" t="n">
-        <v>1865.871540558192</v>
+        <v>1864.336042471607</v>
       </c>
       <c r="U12" t="n">
-        <v>1785.911104741727</v>
+        <v>1784.375606655142</v>
       </c>
       <c r="V12" t="n">
-        <v>1367.213461113929</v>
+        <v>1689.920387269768</v>
       </c>
       <c r="W12" t="n">
-        <v>1254.715336962587</v>
+        <v>1577.422263118426</v>
       </c>
       <c r="X12" t="n">
-        <v>1154.853983987448</v>
+        <v>1477.560910143287</v>
       </c>
       <c r="Y12" t="n">
-        <v>1075.670758971151</v>
+        <v>1398.37768512699</v>
       </c>
     </row>
     <row r="13">
@@ -5166,28 +5166,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6904483778065</v>
       </c>
       <c r="C13" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4824541962423</v>
       </c>
       <c r="D13" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5915983212424</v>
       </c>
       <c r="E13" t="n">
-        <v>798.1069956511426</v>
+        <v>809.2105025326554</v>
       </c>
       <c r="F13" t="n">
-        <v>844.257968243078</v>
+        <v>855.3614751245908</v>
       </c>
       <c r="G13" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1828770770499</v>
       </c>
       <c r="H13" t="n">
-        <v>1016.941316010672</v>
+        <v>1028.044822892185</v>
       </c>
       <c r="I13" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.758226418432</v>
       </c>
       <c r="J13" t="n">
         <v>1505.704370025436</v>
@@ -5223,19 +5223,19 @@
         <v>164.4554332571655</v>
       </c>
       <c r="U13" t="n">
-        <v>321.7272009811524</v>
+        <v>332.8307078626652</v>
       </c>
       <c r="V13" t="n">
-        <v>442.3385938670984</v>
+        <v>453.4421007486112</v>
       </c>
       <c r="W13" t="n">
-        <v>536.0195121267758</v>
+        <v>547.1230190082886</v>
       </c>
       <c r="X13" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y13" t="n">
-        <v>642.0396038300016</v>
+        <v>653.1431107115144</v>
       </c>
     </row>
     <row r="14">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.3814637549632</v>
+        <v>597.7843919601175</v>
       </c>
       <c r="C14" t="n">
-        <v>466.6091624994138</v>
+        <v>468.0120907045681</v>
       </c>
       <c r="D14" t="n">
-        <v>376.36759104502</v>
+        <v>377.7705192501743</v>
       </c>
       <c r="E14" t="n">
-        <v>292.162248007779</v>
+        <v>293.5651762129333</v>
       </c>
       <c r="F14" t="n">
-        <v>207.4252493128175</v>
+        <v>208.8281775179718</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2531916248005</v>
+        <v>126.6561198299548</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>53.32292820515428</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
@@ -5272,49 +5272,49 @@
         <v>135.4535720585666</v>
       </c>
       <c r="K14" t="n">
-        <v>777.9635720585666</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L14" t="n">
-        <v>997.7838685409787</v>
+        <v>955.1539213047977</v>
       </c>
       <c r="M14" t="n">
-        <v>1640.293868540979</v>
+        <v>1597.663921304798</v>
       </c>
       <c r="N14" t="n">
-        <v>1753.464106525702</v>
+        <v>1641.796970190582</v>
       </c>
       <c r="O14" t="n">
-        <v>2395.974106525702</v>
+        <v>1806.950481322281</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2006.976374796579</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2594.597071794846</v>
+        <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.379542772653</v>
+        <v>2452.782470977807</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.241880907853</v>
+        <v>2190.644809113007</v>
       </c>
       <c r="U14" t="n">
-        <v>1857.81891753963</v>
+        <v>1859.221845744784</v>
       </c>
       <c r="V14" t="n">
-        <v>1545.84818605799</v>
+        <v>1547.251114263144</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.268917390366</v>
+        <v>1226.67184559552</v>
       </c>
       <c r="X14" t="n">
-        <v>951.2468633896915</v>
+        <v>952.6497915948457</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.0070323969577</v>
+        <v>760.4099606021121</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>826.2846700948984</v>
+        <v>1009.936718817569</v>
       </c>
       <c r="C15" t="n">
-        <v>785.7797080287173</v>
+        <v>969.4317567513879</v>
       </c>
       <c r="D15" t="n">
-        <v>758.5699232835632</v>
+        <v>617.9795477638095</v>
       </c>
       <c r="E15" t="n">
-        <v>736.678915988702</v>
+        <v>596.0885404689483</v>
       </c>
       <c r="F15" t="n">
-        <v>717.8544287787254</v>
+        <v>577.2640532589717</v>
       </c>
       <c r="G15" t="n">
-        <v>389.5850290955454</v>
+        <v>573.237077818216</v>
       </c>
       <c r="H15" t="n">
-        <v>385.6483296314645</v>
+        <v>245.057954111711</v>
       </c>
       <c r="I15" t="n">
-        <v>385.6483296314645</v>
+        <v>51.92</v>
       </c>
       <c r="J15" t="n">
-        <v>580.0195337690277</v>
+        <v>246.2912041375631</v>
       </c>
       <c r="K15" t="n">
-        <v>889.5622602407697</v>
+        <v>555.8339306093051</v>
       </c>
       <c r="L15" t="n">
-        <v>1322.738028439743</v>
+        <v>989.0096988082788</v>
       </c>
       <c r="M15" t="n">
-        <v>1597.661070182603</v>
+        <v>1263.932740551138</v>
       </c>
       <c r="N15" t="n">
-        <v>1924.781953846775</v>
+        <v>1591.05362421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2341.15068383238</v>
+        <v>2007.422354200916</v>
       </c>
       <c r="P15" t="n">
-        <v>2596</v>
+        <v>2262.271670368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2596</v>
+        <v>2262.271670368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2414.654254688468</v>
+        <v>2079.390426970418</v>
       </c>
       <c r="S15" t="n">
-        <v>2281.744649235363</v>
+        <v>1946.480821517313</v>
       </c>
       <c r="T15" t="n">
-        <v>1875.357445947232</v>
+        <v>1864.336042471607</v>
       </c>
       <c r="U15" t="n">
-        <v>1600.723557932472</v>
+        <v>1784.375606655142</v>
       </c>
       <c r="V15" t="n">
-        <v>1506.268338547098</v>
+        <v>1365.677963027344</v>
       </c>
       <c r="W15" t="n">
-        <v>1393.770214395756</v>
+        <v>1253.179838876002</v>
       </c>
       <c r="X15" t="n">
-        <v>1293.908861420617</v>
+        <v>1153.318485900863</v>
       </c>
       <c r="Y15" t="n">
-        <v>890.4832121618949</v>
+        <v>1074.135260884565</v>
       </c>
     </row>
     <row r="16">
@@ -5403,28 +5403,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6904483778065</v>
       </c>
       <c r="C16" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4824541962423</v>
       </c>
       <c r="D16" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5915983212424</v>
       </c>
       <c r="E16" t="n">
-        <v>798.1069956511426</v>
+        <v>809.2105025326554</v>
       </c>
       <c r="F16" t="n">
-        <v>844.257968243078</v>
+        <v>855.3614751245908</v>
       </c>
       <c r="G16" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1828770770499</v>
       </c>
       <c r="H16" t="n">
-        <v>1016.941316010672</v>
+        <v>1028.044822892185</v>
       </c>
       <c r="I16" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.758226418432</v>
       </c>
       <c r="J16" t="n">
         <v>1505.704370025436</v>
@@ -5448,10 +5448,10 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.6348877086338</v>
+        <v>463.6348877086339</v>
       </c>
       <c r="R16" t="n">
-        <v>82.60111047978445</v>
+        <v>82.60111047978444</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5472,7 +5472,7 @@
         <v>619.9438100324821</v>
       </c>
       <c r="Y16" t="n">
-        <v>642.0396038300016</v>
+        <v>653.1431107115144</v>
       </c>
     </row>
     <row r="17">
@@ -5500,7 +5500,7 @@
         <v>126.6561198299548</v>
       </c>
       <c r="H17" t="n">
-        <v>53.32292820515431</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5509,19 +5509,19 @@
         <v>561.4552612788618</v>
       </c>
       <c r="K17" t="n">
-        <v>1203.965261278862</v>
+        <v>738.645610525093</v>
       </c>
       <c r="L17" t="n">
-        <v>1846.475261278862</v>
+        <v>1381.155610525093</v>
       </c>
       <c r="M17" t="n">
-        <v>1846.475261278862</v>
+        <v>2023.665610525093</v>
       </c>
       <c r="N17" t="n">
-        <v>1846.475261278862</v>
+        <v>2230.820595394003</v>
       </c>
       <c r="O17" t="n">
-        <v>2011.62877241056</v>
+        <v>2395.974106525702</v>
       </c>
       <c r="P17" t="n">
         <v>2596</v>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>687.22979266173</v>
+        <v>1011.472216904154</v>
       </c>
       <c r="C18" t="n">
-        <v>322.4824063531246</v>
+        <v>646.7248305955488</v>
       </c>
       <c r="D18" t="n">
-        <v>100.5991694096744</v>
+        <v>295.2726216079704</v>
       </c>
       <c r="E18" t="n">
         <v>78.70816211481312</v>
@@ -5621,16 +5621,16 @@
         <v>1785.911104741727</v>
       </c>
       <c r="V18" t="n">
-        <v>1367.213461113929</v>
+        <v>1691.455885356353</v>
       </c>
       <c r="W18" t="n">
-        <v>1254.715336962587</v>
+        <v>1578.957761205011</v>
       </c>
       <c r="X18" t="n">
-        <v>1154.853983987448</v>
+        <v>1479.096408229872</v>
       </c>
       <c r="Y18" t="n">
-        <v>751.4283347287266</v>
+        <v>1399.913183213575</v>
       </c>
     </row>
     <row r="19">
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.3814637549632</v>
+        <v>597.7843919601175</v>
       </c>
       <c r="C20" t="n">
-        <v>466.6091624994138</v>
+        <v>468.0120907045681</v>
       </c>
       <c r="D20" t="n">
-        <v>376.36759104502</v>
+        <v>377.7705192501743</v>
       </c>
       <c r="E20" t="n">
-        <v>292.162248007779</v>
+        <v>293.5651762129333</v>
       </c>
       <c r="F20" t="n">
-        <v>207.4252493128175</v>
+        <v>208.8281775179718</v>
       </c>
       <c r="G20" t="n">
-        <v>125.2531916248005</v>
+        <v>126.6561198299548</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>53.32292820515431</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
@@ -5746,19 +5746,19 @@
         <v>135.4535720585666</v>
       </c>
       <c r="K20" t="n">
-        <v>777.9635720585666</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L20" t="n">
-        <v>997.7838685409787</v>
+        <v>945.8005953940028</v>
       </c>
       <c r="M20" t="n">
-        <v>997.7838685409787</v>
+        <v>1588.310595394003</v>
       </c>
       <c r="N20" t="n">
-        <v>1640.293868540979</v>
+        <v>2230.820595394003</v>
       </c>
       <c r="O20" t="n">
-        <v>2282.803868540978</v>
+        <v>2395.974106525702</v>
       </c>
       <c r="P20" t="n">
         <v>2596</v>
@@ -5767,28 +5767,28 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2594.597071794846</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.379542772653</v>
+        <v>2452.782470977807</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.241880907853</v>
+        <v>2190.644809113007</v>
       </c>
       <c r="U20" t="n">
-        <v>1857.81891753963</v>
+        <v>1859.221845744784</v>
       </c>
       <c r="V20" t="n">
-        <v>1545.84818605799</v>
+        <v>1547.251114263144</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.268917390366</v>
+        <v>1226.67184559552</v>
       </c>
       <c r="X20" t="n">
-        <v>951.2468633896915</v>
+        <v>952.6497915948457</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.0070323969577</v>
+        <v>760.4099606021121</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>687.22979266173</v>
+        <v>1141.041188948283</v>
       </c>
       <c r="C21" t="n">
-        <v>322.4824063531246</v>
+        <v>1100.536226882101</v>
       </c>
       <c r="D21" t="n">
-        <v>100.5991694096744</v>
+        <v>749.084017894523</v>
       </c>
       <c r="E21" t="n">
-        <v>78.70816211481312</v>
+        <v>402.9505863572374</v>
       </c>
       <c r="F21" t="n">
         <v>59.88367490483648</v>
@@ -5867,7 +5867,7 @@
         <v>1479.096408229872</v>
       </c>
       <c r="Y21" t="n">
-        <v>1075.670758971151</v>
+        <v>1399.913183213575</v>
       </c>
     </row>
     <row r="22">
@@ -5889,16 +5889,16 @@
         <v>809.2105025326554</v>
       </c>
       <c r="F22" t="n">
-        <v>844.257968243078</v>
+        <v>855.3614751245908</v>
       </c>
       <c r="G22" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1828770770499</v>
       </c>
       <c r="H22" t="n">
-        <v>1016.941316010672</v>
+        <v>1028.044822892185</v>
       </c>
       <c r="I22" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.758226418432</v>
       </c>
       <c r="J22" t="n">
         <v>1505.704370025436</v>
@@ -5974,31 +5974,31 @@
         <v>126.6561198299548</v>
       </c>
       <c r="H23" t="n">
-        <v>53.32292820515428</v>
+        <v>53.32292820515431</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>303.290595394003</v>
+        <v>135.4535720585666</v>
       </c>
       <c r="K23" t="n">
-        <v>945.8005953940029</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L23" t="n">
-        <v>1588.310595394003</v>
+        <v>955.1539213047977</v>
       </c>
       <c r="M23" t="n">
-        <v>2230.820595394003</v>
+        <v>999.286970190582</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.820595394003</v>
+        <v>1641.796970190582</v>
       </c>
       <c r="O23" t="n">
-        <v>2395.974106525702</v>
+        <v>1806.950481322281</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2006.976374796579</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>492.5563404634339</v>
+        <v>1335.714641146579</v>
       </c>
       <c r="C24" t="n">
-        <v>452.0513783972528</v>
+        <v>1100.536226882101</v>
       </c>
       <c r="D24" t="n">
-        <v>424.8415936520986</v>
+        <v>749.084017894523</v>
       </c>
       <c r="E24" t="n">
-        <v>78.70816211481309</v>
+        <v>402.9505863572374</v>
       </c>
       <c r="F24" t="n">
-        <v>59.88367490483647</v>
+        <v>59.88367490483648</v>
       </c>
       <c r="G24" t="n">
-        <v>55.85669946408081</v>
+        <v>55.85669946408083</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6098,13 +6098,13 @@
         <v>1691.455885356353</v>
       </c>
       <c r="W24" t="n">
-        <v>1384.284309006715</v>
+        <v>1578.957761205011</v>
       </c>
       <c r="X24" t="n">
-        <v>960.180531789152</v>
+        <v>1479.096408229872</v>
       </c>
       <c r="Y24" t="n">
-        <v>880.9973067728547</v>
+        <v>1399.913183213575</v>
       </c>
     </row>
     <row r="25">
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6904483778065</v>
       </c>
       <c r="C25" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4824541962423</v>
       </c>
       <c r="D25" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5915983212424</v>
       </c>
       <c r="E25" t="n">
         <v>798.1069956511426</v>
@@ -6159,10 +6159,10 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.6348877086339</v>
+        <v>463.6348877086338</v>
       </c>
       <c r="R25" t="n">
-        <v>82.60111047978444</v>
+        <v>82.60111047978445</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.3814637549632</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C26" t="n">
-        <v>466.6091624994138</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D26" t="n">
-        <v>376.36759104502</v>
+        <v>376.44759104502</v>
       </c>
       <c r="E26" t="n">
-        <v>292.162248007779</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F26" t="n">
-        <v>207.4252493128175</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G26" t="n">
-        <v>125.2531916248006</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H26" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="I26" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>135.4535720585666</v>
+        <v>561.5352612788618</v>
       </c>
       <c r="K26" t="n">
-        <v>312.6439213047977</v>
+        <v>1205.035261278862</v>
       </c>
       <c r="L26" t="n">
-        <v>532.4642177872098</v>
+        <v>1424.855557761274</v>
       </c>
       <c r="M26" t="n">
-        <v>1174.97421778721</v>
+        <v>1424.855557761274</v>
       </c>
       <c r="N26" t="n">
-        <v>1310.98</v>
+        <v>1424.855557761274</v>
       </c>
       <c r="O26" t="n">
-        <v>1953.49</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P26" t="n">
-        <v>2596</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q26" t="n">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2594.597071794846</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.379542772653</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.241880907853</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U26" t="n">
-        <v>1857.81891753963</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V26" t="n">
-        <v>1545.84818605799</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.268917390366</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X26" t="n">
-        <v>951.2468633896915</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.0070323969577</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>687.2297926617302</v>
+        <v>816.8787647058581</v>
       </c>
       <c r="C27" t="n">
-        <v>452.0513783972528</v>
+        <v>776.373802639677</v>
       </c>
       <c r="D27" t="n">
-        <v>424.8415936520986</v>
+        <v>749.1640178945229</v>
       </c>
       <c r="E27" t="n">
-        <v>402.9505863572373</v>
+        <v>727.2730105996617</v>
       </c>
       <c r="F27" t="n">
-        <v>384.1260991472607</v>
+        <v>384.2060991472608</v>
       </c>
       <c r="G27" t="n">
-        <v>55.85669946408081</v>
+        <v>380.1791237065051</v>
       </c>
       <c r="H27" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="I27" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J27" t="n">
-        <v>246.2912041375631</v>
+        <v>246.3712041375631</v>
       </c>
       <c r="K27" t="n">
-        <v>555.8339306093051</v>
+        <v>555.913930609305</v>
       </c>
       <c r="L27" t="n">
-        <v>989.0096988082788</v>
+        <v>989.0896988082787</v>
       </c>
       <c r="M27" t="n">
-        <v>1263.932740551138</v>
+        <v>1264.012740551138</v>
       </c>
       <c r="N27" t="n">
-        <v>1591.05362421531</v>
+        <v>1591.13362421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.502354200916</v>
       </c>
       <c r="P27" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2080.925925057003</v>
+        <v>1886.332472858707</v>
       </c>
       <c r="S27" t="n">
-        <v>1623.773895361475</v>
+        <v>1753.422867405603</v>
       </c>
       <c r="T27" t="n">
-        <v>1541.629116315768</v>
+        <v>1347.035664117471</v>
       </c>
       <c r="U27" t="n">
-        <v>1461.668680499303</v>
+        <v>1267.075228301007</v>
       </c>
       <c r="V27" t="n">
-        <v>1367.213461113929</v>
+        <v>1172.620008915633</v>
       </c>
       <c r="W27" t="n">
-        <v>1254.715336962587</v>
+        <v>1060.121884764291</v>
       </c>
       <c r="X27" t="n">
-        <v>830.6115597450241</v>
+        <v>960.260531789152</v>
       </c>
       <c r="Y27" t="n">
-        <v>751.4283347287268</v>
+        <v>881.0773067728546</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>686.6904483778065</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C28" t="n">
-        <v>734.4824541962423</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D28" t="n">
-        <v>769.5915983212424</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E28" t="n">
-        <v>809.2105025326554</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F28" t="n">
-        <v>844.257968243078</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G28" t="n">
-        <v>920.0793701955371</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H28" t="n">
-        <v>1016.941316010672</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I28" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J28" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.784370025436</v>
       </c>
       <c r="K28" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.533394126239</v>
       </c>
       <c r="L28" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.732180057278</v>
       </c>
       <c r="M28" t="n">
-        <v>1499.938679551308</v>
+        <v>1500.018679551308</v>
       </c>
       <c r="N28" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.864852898339</v>
       </c>
       <c r="O28" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.303511470621</v>
       </c>
       <c r="P28" t="n">
-        <v>819.1796012698439</v>
+        <v>819.2596012698439</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.6348877086339</v>
+        <v>463.7148877086338</v>
       </c>
       <c r="R28" t="n">
-        <v>82.60111047978444</v>
+        <v>82.68111047978445</v>
       </c>
       <c r="S28" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="T28" t="n">
-        <v>164.4554332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U28" t="n">
-        <v>332.8307078626652</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V28" t="n">
-        <v>453.4421007486112</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W28" t="n">
-        <v>547.1230190082886</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X28" t="n">
-        <v>619.9438100324821</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y28" t="n">
-        <v>653.1431107115144</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.3814637549632</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C29" t="n">
-        <v>466.6091624994138</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D29" t="n">
-        <v>376.36759104502</v>
+        <v>376.44759104502</v>
       </c>
       <c r="E29" t="n">
-        <v>292.162248007779</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F29" t="n">
-        <v>207.4252493128175</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G29" t="n">
-        <v>125.2531916248005</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="I29" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>548.7899496653596</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K29" t="n">
-        <v>725.9802989115907</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L29" t="n">
-        <v>945.8005953940028</v>
+        <v>956.2239213047977</v>
       </c>
       <c r="M29" t="n">
-        <v>1588.310595394003</v>
+        <v>1002.296970190582</v>
       </c>
       <c r="N29" t="n">
-        <v>2230.820595394003</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="O29" t="n">
-        <v>2395.974106525702</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q29" t="n">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2594.597071794846</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.379542772653</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.241880907853</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U29" t="n">
-        <v>1857.81891753963</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V29" t="n">
-        <v>1545.84818605799</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.268917390366</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X29" t="n">
-        <v>951.2468633896915</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.0070323969577</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>361.4518703327206</v>
+        <v>1258.035901870889</v>
       </c>
       <c r="C30" t="n">
-        <v>320.9469082665395</v>
+        <v>1217.530939804708</v>
       </c>
       <c r="D30" t="n">
-        <v>293.7371235213853</v>
+        <v>866.0787308171298</v>
       </c>
       <c r="E30" t="n">
-        <v>271.846116226524</v>
+        <v>519.9452992798442</v>
       </c>
       <c r="F30" t="n">
-        <v>253.0216290165474</v>
+        <v>176.8783878274433</v>
       </c>
       <c r="G30" t="n">
-        <v>248.9946535757918</v>
+        <v>172.8514123866877</v>
       </c>
       <c r="H30" t="n">
-        <v>245.057954111711</v>
+        <v>52</v>
       </c>
       <c r="I30" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J30" t="n">
-        <v>246.2912041375631</v>
+        <v>246.3712041375631</v>
       </c>
       <c r="K30" t="n">
-        <v>555.8339306093051</v>
+        <v>555.913930609305</v>
       </c>
       <c r="L30" t="n">
-        <v>989.0096988082788</v>
+        <v>989.0896988082787</v>
       </c>
       <c r="M30" t="n">
-        <v>1263.932740551138</v>
+        <v>1264.012740551138</v>
       </c>
       <c r="N30" t="n">
-        <v>1591.05362421531</v>
+        <v>1591.13362421531</v>
       </c>
       <c r="O30" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.502354200916</v>
       </c>
       <c r="P30" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2262.271670368536</v>
+        <v>2184.592931092847</v>
       </c>
       <c r="R30" t="n">
-        <v>2079.390426970419</v>
+        <v>2003.247185781314</v>
       </c>
       <c r="S30" t="n">
-        <v>1622.23839727489</v>
+        <v>1870.33758032821</v>
       </c>
       <c r="T30" t="n">
-        <v>1540.093618229183</v>
+        <v>1788.192801282503</v>
       </c>
       <c r="U30" t="n">
-        <v>1460.133182412718</v>
+        <v>1708.232365466038</v>
       </c>
       <c r="V30" t="n">
-        <v>1365.677963027344</v>
+        <v>1613.777146080664</v>
       </c>
       <c r="W30" t="n">
-        <v>928.9374146335778</v>
+        <v>1501.279021929322</v>
       </c>
       <c r="X30" t="n">
-        <v>829.0760616584388</v>
+        <v>1401.417668954183</v>
       </c>
       <c r="Y30" t="n">
-        <v>749.8928366421414</v>
+        <v>1322.234443937886</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>675.5869414962938</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C31" t="n">
-        <v>723.3789473147295</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D31" t="n">
-        <v>758.4880914397296</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E31" t="n">
-        <v>798.1069956511426</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F31" t="n">
-        <v>844.257968243078</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G31" t="n">
-        <v>920.0793701955371</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H31" t="n">
-        <v>1016.941316010672</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I31" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J31" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.784370025436</v>
       </c>
       <c r="K31" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.533394126239</v>
       </c>
       <c r="L31" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.732180057278</v>
       </c>
       <c r="M31" t="n">
-        <v>1499.938679551308</v>
+        <v>1500.018679551308</v>
       </c>
       <c r="N31" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.864852898339</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.303511470621</v>
       </c>
       <c r="P31" t="n">
-        <v>819.1796012698439</v>
+        <v>819.2596012698439</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.6348877086338</v>
+        <v>463.7148877086338</v>
       </c>
       <c r="R31" t="n">
-        <v>82.60111047978445</v>
+        <v>82.68111047978445</v>
       </c>
       <c r="S31" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="T31" t="n">
-        <v>164.4554332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U31" t="n">
-        <v>332.8307078626652</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V31" t="n">
-        <v>453.4421007486112</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W31" t="n">
-        <v>547.1230190082886</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X31" t="n">
-        <v>619.9438100324821</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y31" t="n">
-        <v>642.0396038300016</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.3814637549632</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C32" t="n">
-        <v>466.6091624994138</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D32" t="n">
-        <v>376.36759104502</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E32" t="n">
-        <v>292.162248007779</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F32" t="n">
-        <v>207.4252493128175</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G32" t="n">
-        <v>125.2531916248006</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H32" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J32" t="n">
-        <v>135.4535720585666</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K32" t="n">
-        <v>312.6439213047977</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L32" t="n">
-        <v>532.4642177872098</v>
+        <v>947.8205953940028</v>
       </c>
       <c r="M32" t="n">
-        <v>532.4642177872098</v>
+        <v>1591.320595394003</v>
       </c>
       <c r="N32" t="n">
-        <v>1174.97421778721</v>
+        <v>2234.820595394003</v>
       </c>
       <c r="O32" t="n">
-        <v>1364.466374796579</v>
+        <v>2399.974106525702</v>
       </c>
       <c r="P32" t="n">
-        <v>2006.976374796579</v>
+        <v>2600</v>
       </c>
       <c r="Q32" t="n">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="R32" t="n">
-        <v>2594.597071794846</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.379542772653</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.241880907853</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U32" t="n">
-        <v>1857.81891753963</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V32" t="n">
-        <v>1545.84818605799</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.268917390366</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X32" t="n">
-        <v>951.2468633896915</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.0070323969577</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>816.7987647058582</v>
+        <v>1258.035901870889</v>
       </c>
       <c r="C33" t="n">
-        <v>776.2938026396771</v>
+        <v>1100.616226882101</v>
       </c>
       <c r="D33" t="n">
-        <v>749.084017894523</v>
+        <v>1073.406442136947</v>
       </c>
       <c r="E33" t="n">
-        <v>402.9505863572374</v>
+        <v>727.2730105996616</v>
       </c>
       <c r="F33" t="n">
-        <v>59.88367490483647</v>
+        <v>384.2060991472607</v>
       </c>
       <c r="G33" t="n">
-        <v>55.85669946408081</v>
+        <v>55.93669946408081</v>
       </c>
       <c r="H33" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="I33" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>246.2912041375631</v>
+        <v>246.3712041375631</v>
       </c>
       <c r="K33" t="n">
-        <v>555.8339306093051</v>
+        <v>555.913930609305</v>
       </c>
       <c r="L33" t="n">
-        <v>989.0096988082788</v>
+        <v>989.0896988082787</v>
       </c>
       <c r="M33" t="n">
-        <v>1263.932740551138</v>
+        <v>1264.012740551138</v>
       </c>
       <c r="N33" t="n">
-        <v>1591.05362421531</v>
+        <v>1591.13362421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.502354200916</v>
       </c>
       <c r="P33" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2262.271670368536</v>
+        <v>2184.592931092847</v>
       </c>
       <c r="R33" t="n">
-        <v>2080.925925057003</v>
+        <v>2003.247185781314</v>
       </c>
       <c r="S33" t="n">
-        <v>1948.016319603899</v>
+        <v>1870.33758032821</v>
       </c>
       <c r="T33" t="n">
-        <v>1541.629116315768</v>
+        <v>1788.192801282503</v>
       </c>
       <c r="U33" t="n">
-        <v>1461.668680499303</v>
+        <v>1708.232365466038</v>
       </c>
       <c r="V33" t="n">
-        <v>1367.213461113929</v>
+        <v>1613.777146080664</v>
       </c>
       <c r="W33" t="n">
-        <v>1254.715336962587</v>
+        <v>1501.279021929322</v>
       </c>
       <c r="X33" t="n">
-        <v>1154.853983987448</v>
+        <v>1401.417668954183</v>
       </c>
       <c r="Y33" t="n">
-        <v>1075.670758971151</v>
+        <v>1322.234443937886</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>675.5869414962938</v>
+        <v>686.7704483778067</v>
       </c>
       <c r="C34" t="n">
-        <v>723.3789473147295</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D34" t="n">
-        <v>758.4880914397296</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E34" t="n">
-        <v>798.1069956511426</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F34" t="n">
-        <v>844.257968243078</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G34" t="n">
-        <v>920.0793701955371</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H34" t="n">
-        <v>1016.941316010672</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I34" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J34" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.784370025436</v>
       </c>
       <c r="K34" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.533394126239</v>
       </c>
       <c r="L34" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.732180057278</v>
       </c>
       <c r="M34" t="n">
-        <v>1499.938679551308</v>
+        <v>1500.018679551308</v>
       </c>
       <c r="N34" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.864852898339</v>
       </c>
       <c r="O34" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.303511470621</v>
       </c>
       <c r="P34" t="n">
-        <v>819.1796012698439</v>
+        <v>819.2596012698439</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.6348877086339</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R34" t="n">
-        <v>82.60111047978444</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S34" t="n">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="T34" t="n">
-        <v>164.4554332571655</v>
+        <v>164.5354332571655</v>
       </c>
       <c r="U34" t="n">
-        <v>321.7272009811524</v>
+        <v>332.9107078626653</v>
       </c>
       <c r="V34" t="n">
-        <v>442.3385938670984</v>
+        <v>453.5221007486113</v>
       </c>
       <c r="W34" t="n">
-        <v>536.0195121267758</v>
+        <v>547.2030190082887</v>
       </c>
       <c r="X34" t="n">
-        <v>608.8403031509694</v>
+        <v>620.0238100324823</v>
       </c>
       <c r="Y34" t="n">
-        <v>642.0396038300016</v>
+        <v>653.2231107115146</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>450.1875243610247</v>
+        <v>443.7269183004198</v>
       </c>
       <c r="C35" t="n">
-        <v>343.6475463377985</v>
+        <v>338.1970412872946</v>
       </c>
       <c r="D35" t="n">
-        <v>276.638298115728</v>
+        <v>272.1978940753251</v>
       </c>
       <c r="E35" t="n">
-        <v>215.6652783108102</v>
+        <v>212.2349752805083</v>
       </c>
       <c r="F35" t="n">
-        <v>154.160602848172</v>
+        <v>151.7404008279711</v>
       </c>
       <c r="G35" t="n">
-        <v>95.22086839247821</v>
+        <v>93.81076738237834</v>
       </c>
       <c r="H35" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="I35" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J35" t="n">
-        <v>128.6535720585675</v>
+        <v>554.2552612788638</v>
       </c>
       <c r="K35" t="n">
-        <v>687.0135720585786</v>
+        <v>1107.665261278889</v>
       </c>
       <c r="L35" t="n">
-        <v>1245.37357205859</v>
+        <v>1327.485557761301</v>
       </c>
       <c r="M35" t="n">
-        <v>1245.37357205859</v>
+        <v>1517.436488868336</v>
       </c>
       <c r="N35" t="n">
-        <v>1532.486488868337</v>
+        <v>1517.436488868336</v>
       </c>
       <c r="O35" t="n">
-        <v>1697.640000000035</v>
+        <v>1682.590000000035</v>
       </c>
       <c r="P35" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q35" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R35" t="n">
-        <v>2256.000000000066</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="S35" t="n">
-        <v>2136.014794210196</v>
+        <v>2117.024895220275</v>
       </c>
       <c r="T35" t="n">
-        <v>1897.10945557772</v>
+        <v>1879.129657597899</v>
       </c>
       <c r="U35" t="n">
-        <v>1588.91881544182</v>
+        <v>1583.952250872965</v>
       </c>
       <c r="V35" t="n">
-        <v>1300.180407192503</v>
+        <v>1296.223943633749</v>
       </c>
       <c r="W35" t="n">
-        <v>1009.378008299458</v>
+        <v>999.8870992085497</v>
       </c>
       <c r="X35" t="n">
-        <v>758.5882775311064</v>
+        <v>750.1074694502995</v>
       </c>
       <c r="Y35" t="n">
-        <v>589.580769770696</v>
+        <v>582.1100626999901</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>495.581307813246</v>
+        <v>1449.866049684216</v>
       </c>
       <c r="C36" t="n">
-        <v>396.5722089875794</v>
+        <v>1085.11866337561</v>
       </c>
       <c r="D36" t="n">
-        <v>45.12000000000089</v>
+        <v>733.666454388032</v>
       </c>
       <c r="E36" t="n">
-        <v>45.12000000000089</v>
+        <v>387.5330228507465</v>
       </c>
       <c r="F36" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="G36" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="H36" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="I36" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J36" t="n">
-        <v>239.491204137564</v>
+        <v>239.0912041375652</v>
       </c>
       <c r="K36" t="n">
-        <v>549.0339306093059</v>
+        <v>548.6339306093071</v>
       </c>
       <c r="L36" t="n">
-        <v>982.2096988082797</v>
+        <v>981.8096988082808</v>
       </c>
       <c r="M36" t="n">
-        <v>1257.132740551139</v>
+        <v>1256.73274055114</v>
       </c>
       <c r="N36" t="n">
-        <v>1584.253624215311</v>
+        <v>1564.781953846818</v>
       </c>
       <c r="O36" t="n">
-        <v>2000.622354200917</v>
+        <v>1981.150683832424</v>
       </c>
       <c r="P36" t="n">
-        <v>2255.471670368537</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q36" t="n">
-        <v>2255.471670368537</v>
+        <v>2158.241260724355</v>
       </c>
       <c r="R36" t="n">
-        <v>2097.358248289328</v>
+        <v>2001.137939655247</v>
       </c>
       <c r="S36" t="n">
-        <v>1640.206218593799</v>
+        <v>1892.470758444566</v>
       </c>
       <c r="T36" t="n">
-        <v>1233.819015305668</v>
+        <v>1834.568403641284</v>
       </c>
       <c r="U36" t="n">
-        <v>1177.090902721526</v>
+        <v>1778.850392067243</v>
       </c>
       <c r="V36" t="n">
-        <v>1105.868006568475</v>
+        <v>1708.637596924294</v>
       </c>
       <c r="W36" t="n">
-        <v>1016.602205649457</v>
+        <v>1620.381897015376</v>
       </c>
       <c r="X36" t="n">
-        <v>939.973175906641</v>
+        <v>1544.762968282661</v>
       </c>
       <c r="Y36" t="n">
-        <v>884.0222741226669</v>
+        <v>1489.822167508788</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>647.6576774543497</v>
+        <v>276.0487577303654</v>
       </c>
       <c r="C37" t="n">
-        <v>647.6576774543497</v>
+        <v>347.6007635488012</v>
       </c>
       <c r="D37" t="n">
-        <v>647.6576774543497</v>
+        <v>406.4699076738012</v>
       </c>
       <c r="E37" t="n">
-        <v>710.0465816657627</v>
+        <v>469.8488118852143</v>
       </c>
       <c r="F37" t="n">
-        <v>778.9675542576981</v>
+        <v>539.7597844771498</v>
       </c>
       <c r="G37" t="n">
-        <v>778.9675542576981</v>
+        <v>639.3411864296088</v>
       </c>
       <c r="H37" t="n">
-        <v>778.9675542576981</v>
+        <v>759.9631322447441</v>
       </c>
       <c r="I37" t="n">
-        <v>940.7433127506852</v>
+        <v>945.436535770991</v>
       </c>
       <c r="J37" t="n">
-        <v>1290.562963239202</v>
+        <v>1296.246186259508</v>
       </c>
       <c r="K37" t="n">
-        <v>1418.081987340005</v>
+        <v>1424.755210360311</v>
       </c>
       <c r="L37" t="n">
-        <v>1432.225917431017</v>
+        <v>1424.755210360311</v>
       </c>
       <c r="M37" t="n">
-        <v>1353.74474015737</v>
+        <v>1347.284134096765</v>
       </c>
       <c r="N37" t="n">
-        <v>1221.823236736724</v>
+        <v>1216.37273168622</v>
       </c>
       <c r="O37" t="n">
-        <v>1012.494218541329</v>
+        <v>1008.053814500926</v>
       </c>
       <c r="P37" t="n">
-        <v>742.6826315728752</v>
+        <v>739.2523285425733</v>
       </c>
       <c r="Q37" t="n">
-        <v>410.3702412439883</v>
+        <v>407.9500392237874</v>
       </c>
       <c r="R37" t="n">
-        <v>52.56878724746209</v>
+        <v>51.15868623736223</v>
       </c>
       <c r="S37" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="T37" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="U37" t="n">
-        <v>236.2652746055007</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="V37" t="n">
-        <v>379.6466674914466</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="W37" t="n">
-        <v>496.097585751124</v>
+        <v>65.20132836084751</v>
       </c>
       <c r="X37" t="n">
-        <v>591.6883767753175</v>
+        <v>161.782119385041</v>
       </c>
       <c r="Y37" t="n">
-        <v>647.6576774543497</v>
+        <v>218.7414200640733</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>443.6429778187486</v>
+        <v>443.7269183004198</v>
       </c>
       <c r="C38" t="n">
-        <v>337.1029997955225</v>
+        <v>338.1970412872946</v>
       </c>
       <c r="D38" t="n">
-        <v>270.093751573452</v>
+        <v>272.1978940753251</v>
       </c>
       <c r="E38" t="n">
-        <v>209.1207317685341</v>
+        <v>212.2349752805083</v>
       </c>
       <c r="F38" t="n">
-        <v>147.6160563058959</v>
+        <v>151.7404008279711</v>
       </c>
       <c r="G38" t="n">
-        <v>95.22086839247821</v>
+        <v>93.81076738237834</v>
       </c>
       <c r="H38" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="I38" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J38" t="n">
-        <v>128.6535720585675</v>
+        <v>128.2535720585687</v>
       </c>
       <c r="K38" t="n">
-        <v>687.0135720585786</v>
+        <v>305.4439213047998</v>
       </c>
       <c r="L38" t="n">
-        <v>906.8338685409906</v>
+        <v>764.0005953940585</v>
       </c>
       <c r="M38" t="n">
-        <v>1465.193868540995</v>
+        <v>1317.410595394082</v>
       </c>
       <c r="N38" t="n">
-        <v>1465.193868540995</v>
+        <v>1870.820595394105</v>
       </c>
       <c r="O38" t="n">
-        <v>1630.347379672693</v>
+        <v>2035.974106525804</v>
       </c>
       <c r="P38" t="n">
-        <v>1830.373273146992</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="Q38" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="R38" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="S38" t="n">
-        <v>2136.014794210175</v>
+        <v>2129.028027621139</v>
       </c>
       <c r="T38" t="n">
-        <v>1897.109455577698</v>
+        <v>1891.132789998764</v>
       </c>
       <c r="U38" t="n">
-        <v>1588.918815441799</v>
+        <v>1583.952250872965</v>
       </c>
       <c r="V38" t="n">
-        <v>1300.180407192482</v>
+        <v>1296.223943633749</v>
       </c>
       <c r="W38" t="n">
-        <v>1002.833461757182</v>
+        <v>999.8870992085497</v>
       </c>
       <c r="X38" t="n">
-        <v>752.0437309888304</v>
+        <v>750.1074694502995</v>
       </c>
       <c r="Y38" t="n">
-        <v>583.0362232284199</v>
+        <v>582.1100626999901</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>602.5749659108016</v>
+        <v>63.94989832648884</v>
       </c>
       <c r="C39" t="n">
-        <v>585.3023270769437</v>
+        <v>47.68736050273197</v>
       </c>
       <c r="D39" t="n">
-        <v>581.3248655641128</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="E39" t="n">
-        <v>581.3248655641128</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="F39" t="n">
-        <v>238.2579541117118</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="G39" t="n">
-        <v>238.2579541117118</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="H39" t="n">
-        <v>238.2579541117118</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="I39" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J39" t="n">
-        <v>239.491204137564</v>
+        <v>239.0912041375652</v>
       </c>
       <c r="K39" t="n">
-        <v>549.0339306093059</v>
+        <v>548.6339306093071</v>
       </c>
       <c r="L39" t="n">
-        <v>982.2096988082797</v>
+        <v>981.8096988082808</v>
       </c>
       <c r="M39" t="n">
-        <v>1257.132740551139</v>
+        <v>1237.661070182704</v>
       </c>
       <c r="N39" t="n">
-        <v>1584.253624215311</v>
+        <v>1564.781953846876</v>
       </c>
       <c r="O39" t="n">
-        <v>2000.622354200917</v>
+        <v>1981.150683832482</v>
       </c>
       <c r="P39" t="n">
-        <v>2255.471670368537</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="Q39" t="n">
-        <v>2255.471670368537</v>
+        <v>2158.241260724413</v>
       </c>
       <c r="R39" t="n">
-        <v>2097.358248289328</v>
+        <v>2001.137939655305</v>
       </c>
       <c r="S39" t="n">
-        <v>1987.680966068546</v>
+        <v>1892.470758444624</v>
       </c>
       <c r="T39" t="n">
-        <v>1581.293762780415</v>
+        <v>1834.568403641342</v>
       </c>
       <c r="U39" t="n">
-        <v>1524.565650196274</v>
+        <v>1430.365543582453</v>
       </c>
       <c r="V39" t="n">
-        <v>1453.342754043223</v>
+        <v>1011.667899954655</v>
       </c>
       <c r="W39" t="n">
-        <v>1123.595863747012</v>
+        <v>574.9273515608884</v>
       </c>
       <c r="X39" t="n">
-        <v>699.492086529449</v>
+        <v>158.8468169249343</v>
       </c>
       <c r="Y39" t="n">
-        <v>643.5411847454749</v>
+        <v>103.9060161510612</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>839.2804483778075</v>
+        <v>748.0199076738014</v>
       </c>
       <c r="C40" t="n">
-        <v>909.8424541962432</v>
+        <v>748.0199076738014</v>
       </c>
       <c r="D40" t="n">
-        <v>967.7215983212433</v>
+        <v>748.0199076738014</v>
       </c>
       <c r="E40" t="n">
-        <v>1008.302922482167</v>
+        <v>811.3988118852144</v>
       </c>
       <c r="F40" t="n">
-        <v>1077.223895074102</v>
+        <v>881.3097844771498</v>
       </c>
       <c r="G40" t="n">
-        <v>1175.815297026561</v>
+        <v>980.8911864296089</v>
       </c>
       <c r="H40" t="n">
-        <v>1295.447242841697</v>
+        <v>1101.513132244744</v>
       </c>
       <c r="I40" t="n">
-        <v>1295.447242841697</v>
+        <v>1286.986535770991</v>
       </c>
       <c r="J40" t="n">
-        <v>1304.706893330214</v>
+        <v>1296.246186259508</v>
       </c>
       <c r="K40" t="n">
-        <v>1432.225917431017</v>
+        <v>1424.755210360311</v>
       </c>
       <c r="L40" t="n">
-        <v>1432.225917431017</v>
+        <v>1424.755210360311</v>
       </c>
       <c r="M40" t="n">
-        <v>1353.74474015737</v>
+        <v>1347.284134096765</v>
       </c>
       <c r="N40" t="n">
-        <v>1221.823236736724</v>
+        <v>1216.37273168622</v>
       </c>
       <c r="O40" t="n">
-        <v>1012.494218541329</v>
+        <v>1008.053814500926</v>
       </c>
       <c r="P40" t="n">
-        <v>742.6826315728752</v>
+        <v>739.2523285425733</v>
       </c>
       <c r="Q40" t="n">
-        <v>410.3702412439883</v>
+        <v>407.9500392237874</v>
       </c>
       <c r="R40" t="n">
-        <v>52.56878724746209</v>
+        <v>51.15868623736223</v>
       </c>
       <c r="S40" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="T40" t="n">
-        <v>180.4254332571664</v>
+        <v>181.0154332571676</v>
       </c>
       <c r="U40" t="n">
-        <v>371.5707078626662</v>
+        <v>373.1507078626673</v>
       </c>
       <c r="V40" t="n">
-        <v>514.9521007486121</v>
+        <v>517.5221007486133</v>
       </c>
       <c r="W40" t="n">
-        <v>631.4030190082896</v>
+        <v>634.9630190082908</v>
       </c>
       <c r="X40" t="n">
-        <v>726.9938100324831</v>
+        <v>731.5438100324843</v>
       </c>
       <c r="Y40" t="n">
-        <v>782.9631107115154</v>
+        <v>731.5438100324843</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>375.0721638044532</v>
+        <v>459.4091624994159</v>
       </c>
       <c r="C41" t="n">
-        <v>375.0721638044532</v>
+        <v>459.4091624994159</v>
       </c>
       <c r="D41" t="n">
-        <v>284.8305923500595</v>
+        <v>369.1675910450221</v>
       </c>
       <c r="E41" t="n">
-        <v>200.6252493128184</v>
+        <v>284.9622480077811</v>
       </c>
       <c r="F41" t="n">
-        <v>200.6252493128184</v>
+        <v>200.2252493128196</v>
       </c>
       <c r="G41" t="n">
-        <v>118.4531916248014</v>
+        <v>118.0531916248026</v>
       </c>
       <c r="H41" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="I41" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J41" t="n">
-        <v>128.6535720585675</v>
+        <v>128.2535720585687</v>
       </c>
       <c r="K41" t="n">
-        <v>305.8439213047987</v>
+        <v>681.6635720585938</v>
       </c>
       <c r="L41" t="n">
-        <v>525.6642177872108</v>
+        <v>901.4838685410059</v>
       </c>
       <c r="M41" t="n">
-        <v>1084.024217787215</v>
+        <v>1317.410595394067</v>
       </c>
       <c r="N41" t="n">
-        <v>1084.024217787215</v>
+        <v>1870.820595394105</v>
       </c>
       <c r="O41" t="n">
-        <v>1249.177728918913</v>
+        <v>2035.974106525804</v>
       </c>
       <c r="P41" t="n">
-        <v>1807.537728918917</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="Q41" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="R41" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="S41" t="n">
-        <v>2112.782470977852</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.644809113052</v>
+        <v>2052.269579652305</v>
       </c>
       <c r="U41" t="n">
-        <v>1636.50961758912</v>
+        <v>1720.846616284083</v>
       </c>
       <c r="V41" t="n">
-        <v>1324.53888610748</v>
+        <v>1408.875884802442</v>
       </c>
       <c r="W41" t="n">
-        <v>1003.959617439856</v>
+        <v>1088.296616134819</v>
       </c>
       <c r="X41" t="n">
-        <v>729.9375634391815</v>
+        <v>814.2745621341442</v>
       </c>
       <c r="Y41" t="n">
-        <v>537.6977324464477</v>
+        <v>622.0347311414104</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1004.672216904155</v>
+        <v>354.2518703327227</v>
       </c>
       <c r="C42" t="n">
-        <v>639.9248305955498</v>
+        <v>313.7469082665415</v>
       </c>
       <c r="D42" t="n">
-        <v>612.7150458503957</v>
+        <v>286.5371235213873</v>
       </c>
       <c r="E42" t="n">
-        <v>266.5816143131102</v>
+        <v>264.6461162265261</v>
       </c>
       <c r="F42" t="n">
-        <v>247.7571271031335</v>
+        <v>245.8216290165495</v>
       </c>
       <c r="G42" t="n">
-        <v>243.7301516623779</v>
+        <v>241.7946535757938</v>
       </c>
       <c r="H42" t="n">
-        <v>45.12000000000089</v>
+        <v>237.857954111713</v>
       </c>
       <c r="I42" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J42" t="n">
-        <v>239.491204137564</v>
+        <v>239.0912041375652</v>
       </c>
       <c r="K42" t="n">
-        <v>549.0339306093059</v>
+        <v>548.6339306093071</v>
       </c>
       <c r="L42" t="n">
-        <v>982.2096988082797</v>
+        <v>962.7380284398448</v>
       </c>
       <c r="M42" t="n">
-        <v>1257.132740551139</v>
+        <v>1237.661070182704</v>
       </c>
       <c r="N42" t="n">
-        <v>1584.253624215311</v>
+        <v>1564.781953846876</v>
       </c>
       <c r="O42" t="n">
-        <v>2000.622354200917</v>
+        <v>1981.150683832482</v>
       </c>
       <c r="P42" t="n">
-        <v>2255.471670368537</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="Q42" t="n">
-        <v>2255.471670368537</v>
+        <v>2158.241260724413</v>
       </c>
       <c r="R42" t="n">
-        <v>2074.125925057004</v>
+        <v>1652.653091170456</v>
       </c>
       <c r="S42" t="n">
-        <v>1941.2163196039</v>
+        <v>1290.795973032467</v>
       </c>
       <c r="T42" t="n">
-        <v>1859.071540558193</v>
+        <v>884.4087697443359</v>
       </c>
       <c r="U42" t="n">
-        <v>1779.111104741728</v>
+        <v>804.4483339278713</v>
       </c>
       <c r="V42" t="n">
-        <v>1684.655885356354</v>
+        <v>709.9931145424974</v>
       </c>
       <c r="W42" t="n">
-        <v>1247.915336962588</v>
+        <v>597.4949903911555</v>
       </c>
       <c r="X42" t="n">
-        <v>1148.053983987449</v>
+        <v>497.6336374160166</v>
       </c>
       <c r="Y42" t="n">
-        <v>1068.870758971152</v>
+        <v>418.4504123997193</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>668.7869414962947</v>
+        <v>668.3869414962958</v>
       </c>
       <c r="C43" t="n">
-        <v>716.5789473147305</v>
+        <v>716.1789473147315</v>
       </c>
       <c r="D43" t="n">
-        <v>751.6880914397306</v>
+        <v>751.2880914397316</v>
       </c>
       <c r="E43" t="n">
-        <v>791.3069956511436</v>
+        <v>790.9069956511446</v>
       </c>
       <c r="F43" t="n">
-        <v>837.457968243079</v>
+        <v>837.05796824308</v>
       </c>
       <c r="G43" t="n">
-        <v>913.279370195538</v>
+        <v>912.8793701955391</v>
       </c>
       <c r="H43" t="n">
-        <v>1010.141316010673</v>
+        <v>1009.741316010674</v>
       </c>
       <c r="I43" t="n">
-        <v>1171.85471953692</v>
+        <v>1171.454719536921</v>
       </c>
       <c r="J43" t="n">
-        <v>1498.904370025437</v>
+        <v>1498.504370025438</v>
       </c>
       <c r="K43" t="n">
-        <v>1603.65339412624</v>
+        <v>1603.253394126241</v>
       </c>
       <c r="L43" t="n">
-        <v>1594.852180057279</v>
+        <v>1594.45218005728</v>
       </c>
       <c r="M43" t="n">
-        <v>1493.138679551309</v>
+        <v>1492.73867955131</v>
       </c>
       <c r="N43" t="n">
-        <v>1337.98485289834</v>
+        <v>1337.584852898341</v>
       </c>
       <c r="O43" t="n">
-        <v>1105.423511470622</v>
+        <v>1105.023511470623</v>
       </c>
       <c r="P43" t="n">
-        <v>812.3796012698448</v>
+        <v>811.9796012698459</v>
       </c>
       <c r="Q43" t="n">
-        <v>456.8348877086347</v>
+        <v>456.4348877086359</v>
       </c>
       <c r="R43" t="n">
-        <v>75.80111047978534</v>
+        <v>75.40111047978647</v>
       </c>
       <c r="S43" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="T43" t="n">
-        <v>157.6554332571664</v>
+        <v>146.1519263756547</v>
       </c>
       <c r="U43" t="n">
-        <v>326.0307078626662</v>
+        <v>314.5272009811544</v>
       </c>
       <c r="V43" t="n">
-        <v>446.6421007486122</v>
+        <v>435.1385938671004</v>
       </c>
       <c r="W43" t="n">
-        <v>540.3230190082895</v>
+        <v>528.8195121267778</v>
       </c>
       <c r="X43" t="n">
-        <v>613.1438100324831</v>
+        <v>601.6403031509714</v>
       </c>
       <c r="Y43" t="n">
-        <v>646.3431107115154</v>
+        <v>634.8396038300036</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>415.1345492633293</v>
+        <v>589.1814637549653</v>
       </c>
       <c r="C44" t="n">
-        <v>285.3622480077799</v>
+        <v>459.4091624994159</v>
       </c>
       <c r="D44" t="n">
-        <v>285.3622480077799</v>
+        <v>369.1675910450221</v>
       </c>
       <c r="E44" t="n">
-        <v>285.3622480077799</v>
+        <v>284.9622480077811</v>
       </c>
       <c r="F44" t="n">
-        <v>200.6252493128184</v>
+        <v>200.2252493128196</v>
       </c>
       <c r="G44" t="n">
-        <v>118.4531916248014</v>
+        <v>118.0531916248026</v>
       </c>
       <c r="H44" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="I44" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J44" t="n">
-        <v>128.6535720585675</v>
+        <v>554.2552612788638</v>
       </c>
       <c r="K44" t="n">
-        <v>305.8439213047987</v>
+        <v>1097.590298911626</v>
       </c>
       <c r="L44" t="n">
-        <v>525.6642177872108</v>
+        <v>1317.410595394038</v>
       </c>
       <c r="M44" t="n">
-        <v>1084.024217787215</v>
+        <v>1317.410595394038</v>
       </c>
       <c r="N44" t="n">
-        <v>1532.486488868342</v>
+        <v>1870.820595394105</v>
       </c>
       <c r="O44" t="n">
-        <v>1697.640000000041</v>
+        <v>2035.974106525804</v>
       </c>
       <c r="P44" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="Q44" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="R44" t="n">
-        <v>2256.000000000045</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="S44" t="n">
-        <v>2112.782470977852</v>
+        <v>2092.782470977909</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.644809113052</v>
+        <v>2092.782470977909</v>
       </c>
       <c r="U44" t="n">
-        <v>1676.572003047996</v>
+        <v>1761.359507609686</v>
       </c>
       <c r="V44" t="n">
-        <v>1364.601271566356</v>
+        <v>1449.388776128046</v>
       </c>
       <c r="W44" t="n">
-        <v>1044.022002898732</v>
+        <v>1128.809507460422</v>
       </c>
       <c r="X44" t="n">
-        <v>769.9999488980575</v>
+        <v>854.7874534597477</v>
       </c>
       <c r="Y44" t="n">
-        <v>577.7601179053238</v>
+        <v>751.8070323969598</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1003.13671881757</v>
+        <v>1231.684231502455</v>
       </c>
       <c r="C45" t="n">
-        <v>962.6317567513888</v>
+        <v>1191.179269436274</v>
       </c>
       <c r="D45" t="n">
-        <v>611.1795477638104</v>
+        <v>1163.96948469112</v>
       </c>
       <c r="E45" t="n">
-        <v>589.2885404689492</v>
+        <v>1142.078477396259</v>
       </c>
       <c r="F45" t="n">
-        <v>246.2216290165483</v>
+        <v>894.306477501398</v>
       </c>
       <c r="G45" t="n">
-        <v>242.1946535757926</v>
+        <v>566.0370778182181</v>
       </c>
       <c r="H45" t="n">
-        <v>238.2579541117118</v>
+        <v>237.857954111713</v>
       </c>
       <c r="I45" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="J45" t="n">
-        <v>239.491204137564</v>
+        <v>239.0912041375652</v>
       </c>
       <c r="K45" t="n">
-        <v>549.0339306093059</v>
+        <v>548.6339306093071</v>
       </c>
       <c r="L45" t="n">
-        <v>982.2096988082797</v>
+        <v>962.7380284398448</v>
       </c>
       <c r="M45" t="n">
-        <v>1257.132740551139</v>
+        <v>1237.661070182704</v>
       </c>
       <c r="N45" t="n">
-        <v>1584.253624215311</v>
+        <v>1564.781953846876</v>
       </c>
       <c r="O45" t="n">
-        <v>2000.622354200917</v>
+        <v>1981.150683832482</v>
       </c>
       <c r="P45" t="n">
-        <v>2255.471670368537</v>
+        <v>2236.000000000102</v>
       </c>
       <c r="Q45" t="n">
-        <v>2253.936172281951</v>
+        <v>2158.241260724413</v>
       </c>
       <c r="R45" t="n">
-        <v>2072.590426970419</v>
+        <v>1976.89551541288</v>
       </c>
       <c r="S45" t="n">
-        <v>1939.680821517314</v>
+        <v>1843.985909959776</v>
       </c>
       <c r="T45" t="n">
-        <v>1857.536042471607</v>
+        <v>1761.841130914069</v>
       </c>
       <c r="U45" t="n">
-        <v>1777.575606655143</v>
+        <v>1681.880695097604</v>
       </c>
       <c r="V45" t="n">
-        <v>1683.120387269769</v>
+        <v>1587.42547571223</v>
       </c>
       <c r="W45" t="n">
-        <v>1570.622263118427</v>
+        <v>1474.927351560888</v>
       </c>
       <c r="X45" t="n">
-        <v>1146.518485900864</v>
+        <v>1375.065998585749</v>
       </c>
       <c r="Y45" t="n">
-        <v>1067.335260884566</v>
+        <v>1295.882773569452</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>668.786941496295</v>
+        <v>668.3869414962958</v>
       </c>
       <c r="C46" t="n">
-        <v>716.5789473147307</v>
+        <v>716.1789473147315</v>
       </c>
       <c r="D46" t="n">
-        <v>751.6880914397308</v>
+        <v>751.2880914397316</v>
       </c>
       <c r="E46" t="n">
-        <v>791.3069956511438</v>
+        <v>790.9069956511446</v>
       </c>
       <c r="F46" t="n">
-        <v>837.4579682430792</v>
+        <v>837.05796824308</v>
       </c>
       <c r="G46" t="n">
-        <v>913.2793701955383</v>
+        <v>912.8793701955391</v>
       </c>
       <c r="H46" t="n">
-        <v>1010.141316010674</v>
+        <v>1009.741316010674</v>
       </c>
       <c r="I46" t="n">
-        <v>1171.85471953692</v>
+        <v>1171.454719536921</v>
       </c>
       <c r="J46" t="n">
-        <v>1498.904370025437</v>
+        <v>1498.504370025438</v>
       </c>
       <c r="K46" t="n">
-        <v>1603.65339412624</v>
+        <v>1603.253394126241</v>
       </c>
       <c r="L46" t="n">
-        <v>1594.852180057279</v>
+        <v>1594.45218005728</v>
       </c>
       <c r="M46" t="n">
-        <v>1493.138679551309</v>
+        <v>1492.73867955131</v>
       </c>
       <c r="N46" t="n">
-        <v>1337.98485289834</v>
+        <v>1337.584852898341</v>
       </c>
       <c r="O46" t="n">
-        <v>1105.423511470622</v>
+        <v>1105.023511470623</v>
       </c>
       <c r="P46" t="n">
-        <v>812.3796012698449</v>
+        <v>811.9796012698459</v>
       </c>
       <c r="Q46" t="n">
-        <v>456.8348877086348</v>
+        <v>456.4348877086359</v>
       </c>
       <c r="R46" t="n">
-        <v>75.80111047978532</v>
+        <v>75.40111047978647</v>
       </c>
       <c r="S46" t="n">
-        <v>45.12000000000089</v>
+        <v>44.72000000000204</v>
       </c>
       <c r="T46" t="n">
-        <v>157.6554332571664</v>
+        <v>146.1519263756547</v>
       </c>
       <c r="U46" t="n">
-        <v>326.0307078626662</v>
+        <v>314.5272009811544</v>
       </c>
       <c r="V46" t="n">
-        <v>435.5385938670996</v>
+        <v>435.1385938671004</v>
       </c>
       <c r="W46" t="n">
-        <v>529.219512126777</v>
+        <v>528.8195121267778</v>
       </c>
       <c r="X46" t="n">
-        <v>602.0403031509705</v>
+        <v>601.6403031509714</v>
       </c>
       <c r="Y46" t="n">
-        <v>635.2396038300028</v>
+        <v>634.8396038300036</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="M2" t="n">
-        <v>720.3111720492747</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>248.0502805878618</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748744</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>375.1590153027356</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>374.9678606076737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,13 +8678,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>470.019849246231</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>486.4521753063874</v>
+        <v>463.3859690154104</v>
       </c>
       <c r="N11" t="n">
         <v>875.1881540497347</v>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>446.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>20.87871447823917</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>470.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>426.959296482412</v>
       </c>
       <c r="M14" t="n">
         <v>946.1990623156843</v>
       </c>
       <c r="N14" t="n">
-        <v>340.5015257514752</v>
+        <v>270.7669913081025</v>
       </c>
       <c r="O14" t="n">
-        <v>482.1782715841426</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,22 +9152,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>470.019849246231</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>426.9592964824121</v>
       </c>
       <c r="M17" t="n">
-        <v>297.1990623156842</v>
+        <v>946.1990623156843</v>
       </c>
       <c r="N17" t="n">
-        <v>226.1881540497347</v>
+        <v>435.4356135132798</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>388.2276102173145</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>20.87871447823917</v>
@@ -9389,22 +9389,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>470.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>417.5114925321142</v>
       </c>
       <c r="M20" t="n">
-        <v>297.1990623156842</v>
+        <v>946.1990623156843</v>
       </c>
       <c r="N20" t="n">
         <v>875.1881540497347</v>
       </c>
       <c r="O20" t="n">
-        <v>482.1782715841426</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>114.3133717017408</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>20.87871447823917</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>169.5323468034711</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>470.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>426.959296482412</v>
       </c>
       <c r="M23" t="n">
-        <v>946.1990623156843</v>
+        <v>341.7778995740521</v>
       </c>
       <c r="N23" t="n">
-        <v>226.1881540497347</v>
+        <v>875.1881540497347</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>471.0198492462312</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>946.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N26" t="n">
-        <v>363.567732042452</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O26" t="n">
-        <v>482.1782715841426</v>
+        <v>223.1731438679881</v>
       </c>
       <c r="P26" t="n">
-        <v>446.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>417.5114925321141</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>427.959296482412</v>
       </c>
       <c r="M29" t="n">
-        <v>946.1990623156843</v>
+        <v>343.737495533648</v>
       </c>
       <c r="N29" t="n">
-        <v>875.1881540497347</v>
+        <v>876.1881540497347</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,22 +10340,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>419.4710884917101</v>
       </c>
       <c r="M32" t="n">
-        <v>297.1990623156842</v>
+        <v>947.1990623156843</v>
       </c>
       <c r="N32" t="n">
-        <v>875.1881540497347</v>
+        <v>876.1881540497347</v>
       </c>
       <c r="O32" t="n">
-        <v>24.58449078552559</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>446.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,25 +10571,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>385.0198492462423</v>
+        <v>380.0198492462566</v>
       </c>
       <c r="L35" t="n">
-        <v>341.9592964824233</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>297.1990623156842</v>
+        <v>489.0686896965277</v>
       </c>
       <c r="N35" t="n">
-        <v>516.2012013323075</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>361.9536429552635</v>
+        <v>356.9536429552632</v>
       </c>
       <c r="Q35" t="n">
         <v>20.87871447823917</v>
@@ -10662,7 +10662,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>466.1442136678208</v>
       </c>
       <c r="O36" t="n">
         <v>382.6817988009037</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>385.0198492462423</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>241.1478561685319</v>
       </c>
       <c r="M38" t="n">
-        <v>861.1990623156879</v>
+        <v>856.1990623157075</v>
       </c>
       <c r="N38" t="n">
-        <v>226.1881540497347</v>
+        <v>785.1881540497582</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>450.8047011984947</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10896,7 +10896,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
-        <v>471.6948204301074</v>
+        <v>452.4305069266367</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
@@ -11048,25 +11048,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>380.0198492462566</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>861.1990623156879</v>
+        <v>717.3270692379683</v>
       </c>
       <c r="N41" t="n">
-        <v>226.1881540497347</v>
+        <v>785.1881540497727</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>361.9536429552582</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>473.8709074894791</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>388.0893364597981</v>
+        <v>368.8250229563274</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>369.843119582355</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>861.1990623156879</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N44" t="n">
-        <v>679.1803470609747</v>
+        <v>785.1881540498018</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>361.9536429552582</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>20.87871447823917</v>
@@ -11367,7 +11367,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>368.8250229563274</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.041833286308247e-12</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -25176,13 +25176,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>11.88310107685595</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>6.479101076832137</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>6.479101076853294</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>11.88310107679814</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25605,7 +25605,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>83.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -25644,13 +25644,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>77.62316910183324</v>
       </c>
       <c r="U41" t="n">
-        <v>116.1148941258481</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25836,10 +25836,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>89.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>83.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -25884,10 +25884,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U44" t="n">
-        <v>155.7766557301352</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>88.3668158306464</v>
       </c>
     </row>
     <row r="45">
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>948191.3086758077</v>
+        <v>948081.4666758077</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1798270.810900309</v>
+        <v>1798160.968900309</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2648350.313124811</v>
+        <v>2648240.471124811</v>
       </c>
     </row>
     <row r="5">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7747589.177138478</v>
+        <v>7747683.732289992</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8597668.679362975</v>
+        <v>8597763.234514492</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9447748.181587478</v>
+        <v>9447842.736738995</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10289442.37383234</v>
+        <v>10288434.199087</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11139173.75395599</v>
+        <v>11137875.22229065</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11971604.07407964</v>
+        <v>11969262.9654943</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12804034.39420328</v>
+        <v>12800650.70869795</v>
       </c>
     </row>
   </sheetData>
@@ -26281,7 +26281,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="F2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357539</v>
       </c>
       <c r="G2" t="n">
         <v>1353830.31835754</v>
@@ -26290,7 +26290,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="I2" t="n">
-        <v>1353830.318357539</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="J2" t="n">
         <v>1353830.31835754</v>
@@ -26299,19 +26299,19 @@
         <v>1353830.31835754</v>
       </c>
       <c r="L2" t="n">
-        <v>1353830.318357539</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="M2" t="n">
-        <v>1353275.901678395</v>
+        <v>1352813.481398394</v>
       </c>
       <c r="N2" t="n">
-        <v>1353275.901678392</v>
+        <v>1352813.481398398</v>
       </c>
       <c r="O2" t="n">
-        <v>1325722.361678394</v>
+        <v>1324061.961398398</v>
       </c>
       <c r="P2" t="n">
-        <v>1325722.361678393</v>
+        <v>1324061.961398398</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>595400</v>
+        <v>594425</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,13 +26354,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85280.00000000393</v>
+        <v>83968.00000000896</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>238400</v>
+        <v>237600</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.25402263</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>597948.3132650449</v>
       </c>
       <c r="E4" t="n">
-        <v>513253.1653847605</v>
+        <v>513056.3660364837</v>
       </c>
       <c r="F4" t="n">
-        <v>511570.4197316588</v>
+        <v>511373.6203833819</v>
       </c>
       <c r="G4" t="n">
-        <v>509885.3519526902</v>
+        <v>509688.5526044134</v>
       </c>
       <c r="H4" t="n">
-        <v>508197.9453958012</v>
+        <v>508001.1460475244</v>
       </c>
       <c r="I4" t="n">
-        <v>506508.1831919707</v>
+        <v>506311.3838436939</v>
       </c>
       <c r="J4" t="n">
-        <v>504816.0482510949</v>
+        <v>504545.7862134472</v>
       </c>
       <c r="K4" t="n">
-        <v>503121.5232577762</v>
+        <v>502851.9789492135</v>
       </c>
       <c r="L4" t="n">
-        <v>501424.5906669988</v>
+        <v>501155.7651072776</v>
       </c>
       <c r="M4" t="n">
-        <v>505436.0855019955</v>
+        <v>505559.3102707667</v>
       </c>
       <c r="N4" t="n">
-        <v>503674.4115882338</v>
+        <v>503793.1759878661</v>
       </c>
       <c r="O4" t="n">
-        <v>488048.4258486083</v>
+        <v>487559.9239341625</v>
       </c>
       <c r="P4" t="n">
-        <v>486341.4239479526</v>
+        <v>485851.0486090007</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>74075.349</v>
@@ -26449,25 +26449,25 @@
         <v>74075.349</v>
       </c>
       <c r="J5" t="n">
-        <v>74075.349</v>
+        <v>74136.149</v>
       </c>
       <c r="K5" t="n">
-        <v>74075.349</v>
+        <v>74136.149</v>
       </c>
       <c r="L5" t="n">
-        <v>74075.349</v>
+        <v>74136.149</v>
       </c>
       <c r="M5" t="n">
-        <v>70840.93600000069</v>
+        <v>70621.00500000155</v>
       </c>
       <c r="N5" t="n">
-        <v>70840.93600000069</v>
+        <v>70621.00500000155</v>
       </c>
       <c r="O5" t="n">
-        <v>68907.34900000069</v>
+        <v>68603.34900000156</v>
       </c>
       <c r="P5" t="n">
-        <v>68907.34900000069</v>
+        <v>68603.34900000156</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>461722.742147421</v>
+        <v>461177.352506085</v>
       </c>
       <c r="C6" t="n">
-        <v>694829.6643349095</v>
+        <v>695258.7165636913</v>
       </c>
       <c r="D6" t="n">
-        <v>696841.3117507336</v>
+        <v>697269.8050924947</v>
       </c>
       <c r="E6" t="n">
-        <v>171101.8039727798</v>
+        <v>172273.6033210561</v>
       </c>
       <c r="F6" t="n">
-        <v>768184.5496258812</v>
+        <v>768381.3489741572</v>
       </c>
       <c r="G6" t="n">
-        <v>769869.6174048499</v>
+        <v>770066.4167531267</v>
       </c>
       <c r="H6" t="n">
-        <v>771557.023961739</v>
+        <v>771753.8233100154</v>
       </c>
       <c r="I6" t="n">
-        <v>773246.7861655686</v>
+        <v>773443.5855138459</v>
       </c>
       <c r="J6" t="n">
-        <v>386490.9211064447</v>
+        <v>386348.3831440931</v>
       </c>
       <c r="K6" t="n">
-        <v>776633.4460997636</v>
+        <v>776842.1904083266</v>
       </c>
       <c r="L6" t="n">
-        <v>778330.3786905404</v>
+        <v>778538.4042502621</v>
       </c>
       <c r="M6" t="n">
-        <v>691718.8801763945</v>
+        <v>692665.1661276168</v>
       </c>
       <c r="N6" t="n">
-        <v>778760.5540901576</v>
+        <v>778399.3004105302</v>
       </c>
       <c r="O6" t="n">
-        <v>530366.586829785</v>
+        <v>530298.688464234</v>
       </c>
       <c r="P6" t="n">
-        <v>770473.58873044</v>
+        <v>769607.563789396</v>
       </c>
     </row>
   </sheetData>
@@ -26788,10 +26788,10 @@
         <v>321</v>
       </c>
       <c r="M2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>350</v>
@@ -26883,25 +26883,25 @@
         <v>649</v>
       </c>
       <c r="J4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>564.0000000000111</v>
+        <v>559.0000000000255</v>
       </c>
       <c r="N4" t="n">
-        <v>564.0000000000111</v>
+        <v>559.0000000000255</v>
       </c>
       <c r="O4" t="n">
-        <v>564.0000000000111</v>
+        <v>559.0000000000255</v>
       </c>
       <c r="P4" t="n">
-        <v>564.0000000000111</v>
+        <v>559.0000000000255</v>
       </c>
     </row>
   </sheetData>
@@ -26999,19 +26999,19 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>-0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27100,16 +27100,16 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>190.000000000004</v>
+        <v>184.0000000000184</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>223.3220918649895</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>42.44205776706286</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,13 +27566,13 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>30.46477465147608</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>26.19578428848864</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>313.7900811952331</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
@@ -27600,28 +27600,28 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F4" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H4" t="n">
+        <v>227.1197490524383</v>
+      </c>
+      <c r="I4" t="n">
+        <v>171.047816275856</v>
+      </c>
+      <c r="J4" t="n">
+        <v>287.4176955208324</v>
+      </c>
+      <c r="K4" t="n">
         <v>400</v>
       </c>
-      <c r="F4" t="n">
+      <c r="L4" t="n">
         <v>400</v>
-      </c>
-      <c r="G4" t="n">
-        <v>400</v>
-      </c>
-      <c r="H4" t="n">
-        <v>227.1357818393235</v>
-      </c>
-      <c r="I4" t="n">
-        <v>400</v>
-      </c>
-      <c r="J4" t="n">
-        <v>396.2647849014816</v>
-      </c>
-      <c r="K4" t="n">
-        <v>267.1509377355693</v>
-      </c>
-      <c r="L4" t="n">
-        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>293.3820935112229</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>223.3220918649904</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27758,16 +27758,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27809,16 +27809,16 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
+        <v>243.1511452982485</v>
+      </c>
+      <c r="W6" t="n">
         <v>400</v>
       </c>
-      <c r="W6" t="n">
-        <v>58.37314290982852</v>
-      </c>
       <c r="X6" t="n">
-        <v>289.5923456376334</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,37 +27828,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H7" t="n">
+        <v>227.1197490524383</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
       </c>
-      <c r="G7" t="n">
-        <v>244.8599384153005</v>
-      </c>
-      <c r="H7" t="n">
-        <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>171.1020457840527</v>
-      </c>
       <c r="J7" t="n">
-        <v>41.94680253242137</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,16 +27879,16 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>359.1365780635112</v>
+      </c>
+      <c r="T7" t="n">
+        <v>209.2309599488807</v>
+      </c>
+      <c r="U7" t="n">
+        <v>164.8014853870598</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
-      </c>
-      <c r="T7" t="n">
-        <v>400</v>
-      </c>
-      <c r="U7" t="n">
-        <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
@@ -27897,7 +27897,7 @@
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,25 +27986,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135.3862028500681</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>182.7873876361254</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28068,13 +28068,13 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>357.1328808473952</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
@@ -28083,13 +28083,13 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28119,19 +28119,19 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>351.4232471544184</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -28238,10 +28238,10 @@
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>319.4798568942805</v>
+        <v>321</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28271,7 +28271,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>319.4798568942803</v>
       </c>
       <c r="S12" t="n">
         <v>321</v>
@@ -28283,7 +28283,7 @@
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W12" t="n">
         <v>321</v>
@@ -28326,7 +28326,7 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="K13" t="n">
         <v>321</v>
@@ -28359,7 +28359,7 @@
         <v>321</v>
       </c>
       <c r="U13" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="V13" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>95.83643606459415</v>
+        <v>94.44753714149141</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28466,7 +28466,7 @@
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
@@ -28475,13 +28475,13 @@
         <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28508,19 +28508,19 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R15" t="n">
-        <v>321</v>
+        <v>319.4798568942803</v>
       </c>
       <c r="S15" t="n">
         <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>128.2732823236873</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>321</v>
@@ -28529,7 +28529,7 @@
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28563,7 +28563,7 @@
         <v>321</v>
       </c>
       <c r="J16" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="K16" t="n">
         <v>321</v>
@@ -28608,7 +28608,7 @@
         <v>321</v>
       </c>
       <c r="Y16" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17">
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>319.6111010768972</v>
       </c>
       <c r="I17" t="n">
-        <v>94.44753714149138</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>128.2732823236868</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
@@ -28757,7 +28757,7 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W18" t="n">
         <v>321</v>
@@ -28766,7 +28766,7 @@
         <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>95.83643606459415</v>
+        <v>94.44753714149138</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>128.2732823236868</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -29003,7 +29003,7 @@
         <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29025,7 +29025,7 @@
         <v>321</v>
       </c>
       <c r="F22" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
       <c r="G22" t="n">
         <v>321</v>
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>94.44753714149141</v>
+        <v>94.44753714149138</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29234,10 +29234,10 @@
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>128.273282323687</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29250,16 +29250,16 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>321</v>
+      </c>
+      <c r="C25" t="n">
+        <v>321</v>
+      </c>
+      <c r="D25" t="n">
+        <v>321</v>
+      </c>
+      <c r="E25" t="n">
         <v>309.7843364833204</v>
-      </c>
-      <c r="C25" t="n">
-        <v>321</v>
-      </c>
-      <c r="D25" t="n">
-        <v>321</v>
-      </c>
-      <c r="E25" t="n">
-        <v>321</v>
       </c>
       <c r="F25" t="n">
         <v>321</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>161.1050265383575</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29411,7 +29411,7 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>128.2732823236866</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
@@ -29420,13 +29420,13 @@
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>191.2065745705938</v>
@@ -29456,13 +29456,13 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R27" t="n">
-        <v>321</v>
+        <v>128.2732823236866</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>321</v>
@@ -29474,7 +29474,7 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29499,7 +29499,7 @@
         <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
         <v>321</v>
@@ -29541,7 +29541,7 @@
         <v>321</v>
       </c>
       <c r="T28" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U28" t="n">
         <v>321</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>161.1050265383575</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,28 +29645,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>205.2544342066192</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,13 +29690,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>319.4798568942807</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T30" t="n">
         <v>321</v>
@@ -29708,7 +29708,7 @@
         <v>321</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X30" t="n">
         <v>321</v>
@@ -29778,7 +29778,7 @@
         <v>321</v>
       </c>
       <c r="T31" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U31" t="n">
         <v>321</v>
@@ -29793,7 +29793,7 @@
         <v>321</v>
       </c>
       <c r="Y31" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32">
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>161.1050265383575</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>128.2732823236865</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>205.2544342066191</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
@@ -29897,7 +29897,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29936,7 +29936,7 @@
         <v>321</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U33" t="n">
         <v>321</v>
@@ -29964,7 +29964,7 @@
         <v>321</v>
       </c>
       <c r="C34" t="n">
-        <v>321</v>
+        <v>309.7843364833202</v>
       </c>
       <c r="D34" t="n">
         <v>321</v>
@@ -30018,7 +30018,7 @@
         <v>321</v>
       </c>
       <c r="U34" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="V34" t="n">
         <v>321</v>
@@ -30040,25 +30040,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I35" t="n">
         <v>95.83643606459415</v>
@@ -30088,28 +30088,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>162.4939254614814</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="V35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Y35" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36">
@@ -30119,19 +30119,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C36" t="n">
-        <v>263.0809046081093</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0.251349715639833</v>
       </c>
       <c r="G36" t="n">
         <v>324.9867056863481</v>
@@ -30164,31 +30164,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="U36" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="V36" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W36" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X36" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Y36" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37">
@@ -30198,76 +30198,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>345</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G37" t="n">
-        <v>244.4127253005464</v>
+        <v>345</v>
       </c>
       <c r="H37" t="n">
-        <v>223.1596506917826</v>
+        <v>345</v>
       </c>
       <c r="I37" t="n">
-        <v>321.0629848148891</v>
+        <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L37" t="n">
-        <v>344</v>
+        <v>329.713201928271</v>
       </c>
       <c r="M37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T37" t="n">
         <v>207.3278451947823</v>
       </c>
       <c r="U37" t="n">
-        <v>344</v>
+        <v>150.9239650449497</v>
       </c>
       <c r="V37" t="n">
-        <v>344</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>344</v>
+        <v>247.0610203042102</v>
       </c>
       <c r="X37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30277,25 +30277,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I38" t="n">
         <v>95.83643606459415</v>
@@ -30328,25 +30328,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="V38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Y38" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39">
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>324.9867056863481</v>
@@ -30377,7 +30377,7 @@
         <v>324.89733246944</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,31 +30401,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S39" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="U39" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>105.9237215165797</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>7.94301015579299</v>
       </c>
       <c r="Y39" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40">
@@ -30435,76 +30435,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>344</v>
+        <v>303.7563232070959</v>
       </c>
       <c r="C40" t="n">
-        <v>344</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>344</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
-        <v>321.972141363142</v>
+        <v>345</v>
       </c>
       <c r="F40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>157.6531277512658</v>
+        <v>345</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L40" t="n">
         <v>329.713201928271</v>
       </c>
       <c r="M40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="V40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Y40" t="n">
-        <v>344</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30596,13 +30596,13 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
         <v>321</v>
@@ -30611,10 +30611,10 @@
         <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>128.2732823236868</v>
+        <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,16 +30638,16 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>321</v>
+        <v>94.34196244196409</v>
       </c>
       <c r="T42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>321</v>
@@ -30656,7 +30656,7 @@
         <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
@@ -30672,7 +30672,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
       <c r="C43" t="n">
         <v>321</v>
@@ -30726,7 +30726,7 @@
         <v>321</v>
       </c>
       <c r="T43" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U43" t="n">
         <v>321</v>
@@ -30836,19 +30836,19 @@
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>94.34196244196482</v>
       </c>
       <c r="G45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>75.46100877721281</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30896,7 +30896,7 @@
         <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
         <v>321</v>
@@ -30963,13 +30963,13 @@
         <v>321</v>
       </c>
       <c r="T46" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U46" t="n">
         <v>321</v>
       </c>
       <c r="V46" t="n">
-        <v>309.7843364833206</v>
+        <v>321</v>
       </c>
       <c r="W46" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0.1006972724976123</v>
+      </c>
+      <c r="K2" t="n">
+        <v>52.67130150753769</v>
+      </c>
+      <c r="L2" t="n">
+        <v>246.8601159786807</v>
+      </c>
+      <c r="M2" t="n">
         <v>374</v>
-      </c>
-      <c r="K2" t="n">
-        <v>52.15992964824119</v>
-      </c>
-      <c r="L2" t="n">
-        <v>374</v>
-      </c>
-      <c r="M2" t="n">
-        <v>248.0502805878619</v>
       </c>
       <c r="N2" t="n">
         <v>374</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -34886,28 +34886,28 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>265.2804024226294</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.916740661760544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
-        <v>300.210210236103</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
         <v>374</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>19.68201763093985</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>13.85322526014284</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
@@ -35183,7 +35183,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>373.9999999999999</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>294.1798838637633</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35354,34 +35354,34 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>76.15197601043869</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>103.9796017243108</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35457,13 +35457,13 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K11" t="n">
-        <v>178.9801507537688</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>222.040703517588</v>
+        <v>222.0407035175879</v>
       </c>
       <c r="M11" t="n">
-        <v>189.2531129907032</v>
+        <v>166.1869066997263</v>
       </c>
       <c r="N11" t="n">
         <v>649</v>
@@ -35472,7 +35472,7 @@
         <v>166.8217284158573</v>
       </c>
       <c r="P11" t="n">
-        <v>649</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35612,7 +35612,7 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J13" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949537</v>
       </c>
       <c r="K13" t="n">
         <v>105.807095051316</v>
@@ -35645,7 +35645,7 @@
         <v>113.6721548052177</v>
       </c>
       <c r="U13" t="n">
-        <v>158.8603714383706</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V13" t="n">
         <v>121.8296897837838</v>
@@ -35694,25 +35694,25 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K14" t="n">
+        <v>178.9801507537688</v>
+      </c>
+      <c r="L14" t="n">
         <v>649</v>
-      </c>
-      <c r="L14" t="n">
-        <v>222.040703517588</v>
       </c>
       <c r="M14" t="n">
         <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>114.3133717017406</v>
+        <v>44.57883725836777</v>
       </c>
       <c r="O14" t="n">
-        <v>649</v>
+        <v>166.8217284158573</v>
       </c>
       <c r="P14" t="n">
         <v>202.0463570447457</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35840,16 +35840,16 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G16" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H16" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I16" t="n">
         <v>163.3468722487342</v>
       </c>
       <c r="J16" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949537</v>
       </c>
       <c r="K16" t="n">
         <v>105.807095051316</v>
@@ -35894,7 +35894,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.31898363385807</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="17">
@@ -35931,22 +35931,22 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K17" t="n">
-        <v>648.9999999999999</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L17" t="n">
+        <v>649.0000000000001</v>
+      </c>
+      <c r="M17" t="n">
         <v>649</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>209.2474594635451</v>
       </c>
       <c r="O17" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P17" t="n">
-        <v>590.2739672620601</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36168,22 +36168,22 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K20" t="n">
+        <v>178.9801507537688</v>
+      </c>
+      <c r="L20" t="n">
+        <v>639.5521960497022</v>
+      </c>
+      <c r="M20" t="n">
         <v>649</v>
-      </c>
-      <c r="L20" t="n">
-        <v>222.040703517588</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>649</v>
       </c>
       <c r="O20" t="n">
-        <v>649</v>
+        <v>166.8217284158573</v>
       </c>
       <c r="P20" t="n">
-        <v>316.3597287464866</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36311,7 +36311,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F22" t="n">
-        <v>35.40148051557846</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G22" t="n">
         <v>76.58727469945359</v>
@@ -36323,7 +36323,7 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J22" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949537</v>
       </c>
       <c r="K22" t="n">
         <v>105.807095051316</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>253.9096923171747</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L23" t="n">
         <v>649</v>
       </c>
       <c r="M23" t="n">
+        <v>44.57883725836788</v>
+      </c>
+      <c r="N23" t="n">
         <v>649</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>166.8217284158573</v>
@@ -36423,7 +36423,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36536,7 +36536,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.6705361462418</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C25" t="n">
         <v>48.27475335195533</v>
@@ -36545,16 +36545,16 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>40.01909516304346</v>
+        <v>28.80343164636386</v>
       </c>
       <c r="F25" t="n">
         <v>46.61714403225807</v>
       </c>
       <c r="G25" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H25" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I25" t="n">
         <v>163.3468722487342</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K26" t="n">
-        <v>178.9801507537688</v>
+        <v>650</v>
       </c>
       <c r="L26" t="n">
-        <v>222.040703517588</v>
+        <v>222.0407035175879</v>
       </c>
       <c r="M26" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>137.3795779927173</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>649</v>
+        <v>389.9948722838454</v>
       </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36785,13 +36785,13 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>35.40148051557846</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H28" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I28" t="n">
         <v>163.3468722487342</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U28" t="n">
         <v>170.0760349550503</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>501.8888380458177</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K29" t="n">
         <v>178.9801507537688</v>
       </c>
       <c r="L29" t="n">
-        <v>222.040703517588</v>
+        <v>650</v>
       </c>
       <c r="M29" t="n">
-        <v>649</v>
+        <v>46.5384332179639</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O29" t="n">
         <v>166.8217284158573</v>
@@ -36897,7 +36897,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U31" t="n">
         <v>170.0760349550503</v>
@@ -37079,7 +37079,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y31" t="n">
-        <v>22.31898363385807</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="32">
@@ -37119,22 +37119,22 @@
         <v>178.9801507537688</v>
       </c>
       <c r="L32" t="n">
-        <v>222.040703517588</v>
+        <v>641.5117920092981</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="N32" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O32" t="n">
-        <v>191.4062192013829</v>
+        <v>166.8217284158573</v>
       </c>
       <c r="P32" t="n">
-        <v>649</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q32" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37250,7 +37250,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C34" t="n">
-        <v>48.27475335195533</v>
+        <v>37.05908983527552</v>
       </c>
       <c r="D34" t="n">
         <v>35.46378194444452</v>
@@ -37304,7 +37304,7 @@
         <v>113.6721548052177</v>
       </c>
       <c r="U34" t="n">
-        <v>158.8603714383706</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V34" t="n">
         <v>121.8296897837838</v>
@@ -37350,25 +37350,25 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K35" t="n">
-        <v>564.0000000000111</v>
+        <v>559.0000000000255</v>
       </c>
       <c r="L35" t="n">
-        <v>564.0000000000113</v>
+        <v>222.0407035175879</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>191.8696273808436</v>
       </c>
       <c r="N35" t="n">
-        <v>290.0130472825728</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P35" t="n">
-        <v>564.0000000000092</v>
+        <v>559.0000000000089</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37441,7 +37441,7 @@
         <v>277.7000421645042</v>
       </c>
       <c r="N36" t="n">
-        <v>330.4251350143152</v>
+        <v>311.1608215107858</v>
       </c>
       <c r="O36" t="n">
         <v>420.5744747329351</v>
@@ -37484,37 +37484,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>63.01909516304346</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>69.61714403225807</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>100.5872746994536</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>121.8403493082175</v>
       </c>
       <c r="I37" t="n">
-        <v>163.4098570636233</v>
+        <v>187.3468722487342</v>
       </c>
       <c r="J37" t="n">
-        <v>353.3531823116332</v>
+        <v>354.3531823116332</v>
       </c>
       <c r="K37" t="n">
-        <v>128.807095051316</v>
+        <v>129.807095051316</v>
       </c>
       <c r="L37" t="n">
-        <v>14.28679807172902</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,19 +37541,19 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>193.0760349550503</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>144.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>117.6271901612903</v>
+        <v>20.68821046550048</v>
       </c>
       <c r="X37" t="n">
-        <v>96.55635456989245</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>56.53464715053764</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37590,16 +37590,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K38" t="n">
-        <v>564.0000000000111</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L38" t="n">
-        <v>222.040703517588</v>
+        <v>463.1885596861199</v>
       </c>
       <c r="M38" t="n">
-        <v>564.0000000000039</v>
+        <v>559.0000000000234</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>559.0000000000234</v>
       </c>
       <c r="O38" t="n">
         <v>166.8217284158573</v>
@@ -37608,7 +37608,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q38" t="n">
-        <v>429.9259867202556</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37675,7 +37675,7 @@
         <v>437.5512810090644</v>
       </c>
       <c r="M39" t="n">
-        <v>277.7000421645042</v>
+        <v>258.4357286610335</v>
       </c>
       <c r="N39" t="n">
         <v>330.4251350143152</v>
@@ -37721,34 +37721,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>56.88619966292134</v>
+        <v>16.64252287001727</v>
       </c>
       <c r="C40" t="n">
-        <v>71.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>58.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>40.99123652618545</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>69.61714403225807</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>99.58727469945357</v>
+        <v>100.5872746994536</v>
       </c>
       <c r="H40" t="n">
-        <v>120.8403493082175</v>
+        <v>121.8403493082175</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>187.3468722487342</v>
       </c>
       <c r="J40" t="n">
         <v>9.353182311633219</v>
       </c>
       <c r="K40" t="n">
-        <v>128.807095051316</v>
+        <v>129.807095051316</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>136.6721548052177</v>
+        <v>137.6721548052177</v>
       </c>
       <c r="U40" t="n">
-        <v>193.0760349550503</v>
+        <v>194.0760349550503</v>
       </c>
       <c r="V40" t="n">
-        <v>144.8296897837838</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>117.6271901612903</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>96.55635456989245</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>56.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37827,25 +37827,25 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K41" t="n">
-        <v>178.9801507537689</v>
+        <v>559.0000000000255</v>
       </c>
       <c r="L41" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M41" t="n">
-        <v>564.0000000000039</v>
+        <v>420.1280069222841</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>559.000000000038</v>
       </c>
       <c r="O41" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P41" t="n">
-        <v>564.0000000000039</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q41" t="n">
-        <v>452.9921930112399</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L42" t="n">
-        <v>437.5512810090644</v>
+        <v>418.2869675055937</v>
       </c>
       <c r="M42" t="n">
         <v>277.7000421645042</v>
@@ -37958,7 +37958,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.6705361462418</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C43" t="n">
         <v>48.27475335195533</v>
@@ -37973,10 +37973,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H43" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I43" t="n">
         <v>163.3468722487342</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U43" t="n">
         <v>170.0760349550503</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K44" t="n">
-        <v>178.9801507537689</v>
+        <v>548.8232703361239</v>
       </c>
       <c r="L44" t="n">
-        <v>222.040703517588</v>
+        <v>222.0407035175879</v>
       </c>
       <c r="M44" t="n">
-        <v>564.0000000000039</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>452.9921930112399</v>
+        <v>559.0000000000671</v>
       </c>
       <c r="O44" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P44" t="n">
-        <v>564.0000000000039</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38146,7 +38146,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L45" t="n">
-        <v>437.5512810090644</v>
+        <v>418.2869675055937</v>
       </c>
       <c r="M45" t="n">
         <v>277.7000421645042</v>
@@ -38249,13 +38249,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U46" t="n">
         <v>170.0760349550503</v>
       </c>
       <c r="V46" t="n">
-        <v>110.6140262671044</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W46" t="n">
         <v>94.62719016129032</v>
